--- a/SauceDemoTC&BR.xlsx
+++ b/SauceDemoTC&BR.xlsx
@@ -3960,22 +3960,22 @@
       </c>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="27" t="s">
+      <c r="A206" s="94" t="s">
         <v>126</v>
       </c>
-      <c r="B206" s="41">
+      <c r="B206" s="95">
         <v>18000</v>
       </c>
-      <c r="C206" s="42" t="s">
+      <c r="C206" s="96" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="207" spans="1:3">
-      <c r="A207" s="27" t="s">
+      <c r="A207" s="94" t="s">
         <v>136</v>
       </c>
-      <c r="B207" s="27"/>
-      <c r="C207" s="42" t="s">
+      <c r="B207" s="94"/>
+      <c r="C207" s="96" t="s">
         <v>132</v>
       </c>
     </row>

--- a/SauceDemoTC&BR.xlsx
+++ b/SauceDemoTC&BR.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="296">
   <si>
     <t>ID</t>
   </si>
@@ -862,6 +862,126 @@
       </rPr>
       <t>“Epic sadface: Sorry, this user has been locked out.”</t>
     </r>
+  </si>
+  <si>
+    <t>Test Case - Naigation Section</t>
+  </si>
+  <si>
+    <t>TC-NAV-1</t>
+  </si>
+  <si>
+    <t>Verify that burger menu opens</t>
+  </si>
+  <si>
+    <t>User is logged in, on inventory page</t>
+  </si>
+  <si>
+    <t>Click burger menu (three vertical lines in the upper left corner)</t>
+  </si>
+  <si>
+    <t>Side navigation panel opens with options: All Items, About, Logout, Reset App State</t>
+  </si>
+  <si>
+    <t>Verify Logout option</t>
+  </si>
+  <si>
+    <t>TC-NAV-2</t>
+  </si>
+  <si>
+    <t>Click Logout</t>
+  </si>
+  <si>
+    <t>Click burger menu</t>
+  </si>
+  <si>
+    <t>User is redirected to Sauce Labs login page</t>
+  </si>
+  <si>
+    <t>TC-NAV-3</t>
+  </si>
+  <si>
+    <t>Click About</t>
+  </si>
+  <si>
+    <t>User is redirected to Sauce Labs website</t>
+  </si>
+  <si>
+    <t>TC-NAV-4</t>
+  </si>
+  <si>
+    <t>Verifay About option</t>
+  </si>
+  <si>
+    <t>Verify Reset App State option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click Reset App State option </t>
+  </si>
+  <si>
+    <t>Cart is emptied, product buttons reset to “Add to cart”</t>
+  </si>
+  <si>
+    <t>TC-NAV-5</t>
+  </si>
+  <si>
+    <t>Verify All Item option</t>
+  </si>
+  <si>
+    <t>User is logged in, on invenory page</t>
+  </si>
+  <si>
+    <t>User is redirected back to inventory page</t>
+  </si>
+  <si>
+    <t>Verify burger menu closes when clicking outside panel</t>
+  </si>
+  <si>
+    <t>TC-NAV-6</t>
+  </si>
+  <si>
+    <t>User is logged in, burger menu opened</t>
+  </si>
+  <si>
+    <t>Click outside of burger menu panel</t>
+  </si>
+  <si>
+    <t>Burger menu closes</t>
+  </si>
+  <si>
+    <t>Verify navigation options are visible and clickable</t>
+  </si>
+  <si>
+    <t>TC-NAV-7</t>
+  </si>
+  <si>
+    <t>TC-NAV-8</t>
+  </si>
+  <si>
+    <t>Side navigation panel opens</t>
+  </si>
+  <si>
+    <t>Observe navigation options in the panel</t>
+  </si>
+  <si>
+    <t>Options All Items, About, Logout, Reset App State are visible and not overlapping</t>
+  </si>
+  <si>
+    <t>Verify that burger menu closes when clicking X button</t>
+  </si>
+  <si>
+    <t>User is logged in and burger menu is opened on inventory page</t>
+  </si>
+  <si>
+    <t>Click on the X button in the top right corner of the opened burger menu</t>
+  </si>
+  <si>
+    <t>Burger menu closes immediately, navigation panel disappears</t>
+  </si>
+  <si>
+    <t>Observe page after closing</t>
+  </si>
+  <si>
+    <t>User remains on inventory page, layout is intact, no overlapping or broken elements</t>
   </si>
 </sst>
 </file>
@@ -996,7 +1116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -1375,11 +1495,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1523,101 +1676,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1642,6 +1705,141 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1760,13 +1958,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>332</xdr:row>
+      <xdr:row>339</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>332</xdr:row>
+      <xdr:row>339</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1777,6 +1975,241 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9204960" y="15803880"/>
+          <a:ext cx="601980" cy="7620"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>330</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>330</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Straight Arrow Connector 5"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9204960" y="62567820"/>
+          <a:ext cx="601980" cy="7620"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>316</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>316</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9204960" y="62567820"/>
+          <a:ext cx="601980" cy="7620"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>305</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>305</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Straight Arrow Connector 7"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9204960" y="62567820"/>
+          <a:ext cx="601980" cy="7620"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>294</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>294</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Arrow Connector 8"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9204960" y="62567820"/>
+          <a:ext cx="601980" cy="7620"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>264</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>264</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Straight Arrow Connector 9"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9204960" y="62567820"/>
           <a:ext cx="601980" cy="7620"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2287,7 +2720,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2295,7 +2728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E336"/>
+  <dimension ref="A1:E394"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="39.77734375" style="8" bestFit="1" customWidth="1"/>
@@ -2306,30 +2739,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="E1" s="60" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="72"/>
+      <c r="E1" s="91" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="67"/>
-      <c r="E2" s="61"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="75"/>
+      <c r="E2" s="92"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="59"/>
-      <c r="E5" s="55" t="s">
+      <c r="C5" s="76"/>
+      <c r="E5" s="67" t="s">
         <v>218</v>
       </c>
     </row>
@@ -2337,21 +2770,21 @@
       <c r="A6" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="E6" s="56"/>
+      <c r="C6" s="77"/>
+      <c r="E6" s="68"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="59"/>
-      <c r="E7" s="56"/>
+      <c r="C7" s="76"/>
+      <c r="E7" s="68"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="18" t="s">
@@ -2363,7 +2796,7 @@
       <c r="C8" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="56"/>
+      <c r="E8" s="68"/>
     </row>
     <row r="9" spans="1:5" ht="27">
       <c r="A9" s="19" t="s">
@@ -2376,7 +2809,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="51"/>
-      <c r="E9" s="56"/>
+      <c r="E9" s="68"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="19" t="s">
@@ -2388,7 +2821,7 @@
       <c r="C10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="56"/>
+      <c r="E10" s="68"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="19" t="s">
@@ -2400,7 +2833,7 @@
       <c r="C11" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="56"/>
+      <c r="E11" s="68"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="19" t="s">
@@ -2412,7 +2845,7 @@
       <c r="C12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="57"/>
+      <c r="E12" s="69"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="9"/>
@@ -2423,28 +2856,28 @@
       <c r="A15" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="59" t="s">
+      <c r="B15" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="59"/>
+      <c r="C15" s="76"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="77"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="59" t="s">
+      <c r="B17" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="59"/>
+      <c r="C17" s="76"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="18" t="s">
@@ -2494,28 +2927,28 @@
       <c r="A23" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="59" t="s">
+      <c r="B23" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="59"/>
+      <c r="C23" s="76"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="58"/>
+      <c r="C24" s="77"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="59" t="s">
+      <c r="B25" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="59"/>
+      <c r="C25" s="76"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="18" t="s">
@@ -2565,28 +2998,28 @@
       <c r="A31" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="59"/>
+      <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="58" t="s">
+      <c r="B32" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="58"/>
+      <c r="C32" s="77"/>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="59" t="s">
+      <c r="B33" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="59"/>
+      <c r="C33" s="76"/>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="18" t="s">
@@ -2636,28 +3069,28 @@
       <c r="A40" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="59" t="s">
+      <c r="B40" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="76"/>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B41" s="58" t="s">
+      <c r="B41" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="C41" s="58"/>
+      <c r="C41" s="77"/>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="59" t="s">
+      <c r="B42" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="59"/>
+      <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="18" t="s">
@@ -2707,28 +3140,28 @@
       <c r="A48" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="59" t="s">
+      <c r="B48" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="C48" s="59"/>
+      <c r="C48" s="76"/>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="58" t="s">
+      <c r="B49" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="58"/>
+      <c r="C49" s="77"/>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="59" t="s">
+      <c r="B50" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="59"/>
+      <c r="C50" s="76"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="18" t="s">
@@ -2778,28 +3211,28 @@
       <c r="A56" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B56" s="59" t="s">
+      <c r="B56" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="59"/>
+      <c r="C56" s="76"/>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B57" s="58" t="s">
+      <c r="B57" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="C57" s="58"/>
+      <c r="C57" s="77"/>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B58" s="59" t="s">
+      <c r="B58" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C58" s="59"/>
+      <c r="C58" s="76"/>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="18" t="s">
@@ -2849,28 +3282,28 @@
       <c r="A64" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B64" s="59" t="s">
+      <c r="B64" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="C64" s="59"/>
+      <c r="C64" s="76"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B65" s="58" t="s">
+      <c r="B65" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="C65" s="58"/>
+      <c r="C65" s="77"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B66" s="59" t="s">
+      <c r="B66" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C66" s="59"/>
+      <c r="C66" s="76"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="18" t="s">
@@ -2909,28 +3342,28 @@
       <c r="A71" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B71" s="59" t="s">
+      <c r="B71" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="C71" s="59"/>
+      <c r="C71" s="76"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B72" s="58" t="s">
+      <c r="B72" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="C72" s="58"/>
+      <c r="C72" s="77"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B73" s="59" t="s">
+      <c r="B73" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C73" s="59"/>
+      <c r="C73" s="76"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="18" t="s">
@@ -2985,11 +3418,11 @@
       <c r="A79" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B79" s="59" t="s">
+      <c r="B79" s="76" t="s">
         <v>220</v>
       </c>
-      <c r="C79" s="59"/>
-      <c r="E79" s="55" t="s">
+      <c r="C79" s="76"/>
+      <c r="E79" s="67" t="s">
         <v>218</v>
       </c>
     </row>
@@ -2997,21 +3430,21 @@
       <c r="A80" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B80" s="58" t="s">
+      <c r="B80" s="77" t="s">
         <v>221</v>
       </c>
-      <c r="C80" s="58"/>
-      <c r="E80" s="56"/>
+      <c r="C80" s="77"/>
+      <c r="E80" s="68"/>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B81" s="59" t="s">
+      <c r="B81" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="C81" s="59"/>
-      <c r="E81" s="56"/>
+      <c r="C81" s="76"/>
+      <c r="E81" s="68"/>
     </row>
     <row r="82" spans="1:5" ht="14.4" customHeight="1">
       <c r="A82" s="18" t="s">
@@ -3023,7 +3456,7 @@
       <c r="C82" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E82" s="56"/>
+      <c r="E82" s="68"/>
     </row>
     <row r="83" spans="1:5" ht="29.4">
       <c r="A83" s="53" t="s">
@@ -3033,56 +3466,56 @@
       <c r="C83" s="54" t="s">
         <v>224</v>
       </c>
-      <c r="E83" s="56"/>
+      <c r="E83" s="68"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="14"/>
       <c r="B84" s="52"/>
       <c r="C84" s="14"/>
-      <c r="E84" s="56"/>
+      <c r="E84" s="68"/>
     </row>
     <row r="85" spans="1:5" ht="15" thickBot="1">
-      <c r="E85" s="56"/>
+      <c r="E85" s="68"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="62" t="s">
+      <c r="A86" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="B86" s="63"/>
-      <c r="C86" s="64"/>
-      <c r="E86" s="57"/>
+      <c r="B86" s="71"/>
+      <c r="C86" s="72"/>
+      <c r="E86" s="69"/>
     </row>
     <row r="87" spans="1:5" ht="15" thickBot="1">
-      <c r="A87" s="65"/>
-      <c r="B87" s="66"/>
-      <c r="C87" s="67"/>
+      <c r="A87" s="73"/>
+      <c r="B87" s="74"/>
+      <c r="C87" s="75"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B90" s="59" t="s">
+      <c r="B90" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="C90" s="59"/>
+      <c r="C90" s="76"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B91" s="58" t="s">
+      <c r="B91" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="C91" s="58"/>
+      <c r="C91" s="77"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B92" s="59" t="s">
+      <c r="B92" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="C92" s="59"/>
+      <c r="C92" s="76"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="18" t="s">
@@ -3102,7 +3535,7 @@
       <c r="B94" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C94" s="59" t="s">
+      <c r="C94" s="76" t="s">
         <v>61</v>
       </c>
     </row>
@@ -3113,7 +3546,7 @@
       <c r="B95" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C95" s="59"/>
+      <c r="C95" s="76"/>
     </row>
     <row r="96" spans="1:5" ht="15" thickBot="1">
       <c r="A96" s="11"/>
@@ -3124,28 +3557,28 @@
       <c r="A98" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B98" s="59" t="s">
+      <c r="B98" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="C98" s="59"/>
+      <c r="C98" s="76"/>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B99" s="58" t="s">
+      <c r="B99" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="C99" s="58"/>
+      <c r="C99" s="77"/>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B100" s="59" t="s">
+      <c r="B100" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="C100" s="59"/>
+      <c r="C100" s="76"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="18" t="s">
@@ -3178,28 +3611,28 @@
       <c r="A105" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B105" s="59" t="s">
+      <c r="B105" s="76" t="s">
         <v>66</v>
       </c>
-      <c r="C105" s="59"/>
+      <c r="C105" s="76"/>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B106" s="58" t="s">
+      <c r="B106" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="C106" s="58"/>
+      <c r="C106" s="77"/>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B107" s="59" t="s">
+      <c r="B107" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="C107" s="59"/>
+      <c r="C107" s="76"/>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="18" t="s">
@@ -3230,28 +3663,28 @@
       <c r="A112" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B112" s="59" t="s">
+      <c r="B112" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C112" s="59"/>
+      <c r="C112" s="76"/>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B113" s="58" t="s">
+      <c r="B113" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="C113" s="58"/>
+      <c r="C113" s="77"/>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B114" s="59" t="s">
+      <c r="B114" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="C114" s="59"/>
+      <c r="C114" s="76"/>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="18" t="s">
@@ -3271,7 +3704,7 @@
       <c r="B116" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C116" s="59" t="s">
+      <c r="C116" s="76" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3282,7 +3715,7 @@
       <c r="B117" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C117" s="59"/>
+      <c r="C117" s="76"/>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="19" t="s">
@@ -3291,34 +3724,34 @@
       <c r="B118" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C118" s="59"/>
+      <c r="C118" s="76"/>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B121" s="59" t="s">
+      <c r="B121" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="C121" s="59"/>
+      <c r="C121" s="76"/>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B122" s="58" t="s">
+      <c r="B122" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="C122" s="58"/>
+      <c r="C122" s="77"/>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B123" s="59" t="s">
+      <c r="B123" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="C123" s="59"/>
+      <c r="C123" s="76"/>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="18" t="s">
@@ -3351,28 +3784,28 @@
       <c r="A128" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B128" s="59" t="s">
+      <c r="B128" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C128" s="59"/>
+      <c r="C128" s="76"/>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B129" s="58" t="s">
+      <c r="B129" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="C129" s="58"/>
+      <c r="C129" s="77"/>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B130" s="59" t="s">
+      <c r="B130" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="C130" s="59"/>
+      <c r="C130" s="76"/>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="18" t="s">
@@ -3392,7 +3825,7 @@
       <c r="B132" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C132" s="59" t="s">
+      <c r="C132" s="76" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3403,7 +3836,7 @@
       <c r="B133" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C133" s="59"/>
+      <c r="C133" s="76"/>
     </row>
     <row r="134" spans="1:3" ht="15" thickBot="1">
       <c r="A134" s="11"/>
@@ -3414,28 +3847,28 @@
       <c r="A136" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B136" s="59" t="s">
+      <c r="B136" s="76" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="59"/>
+      <c r="C136" s="76"/>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B137" s="58" t="s">
+      <c r="B137" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="C137" s="58"/>
+      <c r="C137" s="77"/>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B138" s="59" t="s">
+      <c r="B138" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="C138" s="59"/>
+      <c r="C138" s="76"/>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="18" t="s">
@@ -3455,7 +3888,7 @@
       <c r="B140" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C140" s="59" t="s">
+      <c r="C140" s="76" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3466,7 +3899,7 @@
       <c r="B141" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C141" s="59"/>
+      <c r="C141" s="76"/>
     </row>
     <row r="142" spans="1:3" ht="15" thickBot="1">
       <c r="A142" s="11"/>
@@ -3477,28 +3910,28 @@
       <c r="A144" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B144" s="59" t="s">
+      <c r="B144" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="C144" s="59"/>
+      <c r="C144" s="76"/>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B145" s="58" t="s">
+      <c r="B145" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="C145" s="58"/>
+      <c r="C145" s="77"/>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B146" s="59" t="s">
+      <c r="B146" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="C146" s="59"/>
+      <c r="C146" s="76"/>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="18" t="s">
@@ -3518,7 +3951,7 @@
       <c r="B148" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C148" s="59" t="s">
+      <c r="C148" s="76" t="s">
         <v>89</v>
       </c>
     </row>
@@ -3529,7 +3962,7 @@
       <c r="B149" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C149" s="59"/>
+      <c r="C149" s="76"/>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="10"/>
@@ -3540,28 +3973,28 @@
       <c r="A151" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B151" s="59" t="s">
+      <c r="B151" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="C151" s="59"/>
+      <c r="C151" s="76"/>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B152" s="58" t="s">
+      <c r="B152" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="C152" s="58"/>
+      <c r="C152" s="77"/>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B153" s="59" t="s">
+      <c r="B153" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="C153" s="59"/>
+      <c r="C153" s="76"/>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" s="18" t="s">
@@ -3581,14 +4014,14 @@
       <c r="B155" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C155" s="59" t="s">
+      <c r="C155" s="76" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" s="19"/>
       <c r="B156" s="20"/>
-      <c r="C156" s="59"/>
+      <c r="C156" s="76"/>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="19" t="s">
@@ -3597,633 +4030,657 @@
       <c r="B157" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C157" s="59"/>
+      <c r="C157" s="76"/>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="14"/>
       <c r="B158" s="15"/>
       <c r="C158" s="16"/>
     </row>
+    <row r="159" spans="1:3">
+      <c r="A159" s="79" t="s">
+        <v>256</v>
+      </c>
+      <c r="B159" s="79"/>
+      <c r="C159" s="79"/>
+    </row>
     <row r="160" spans="1:3">
-      <c r="A160" s="68" t="s">
-        <v>169</v>
-      </c>
-      <c r="B160" s="68"/>
-      <c r="C160" s="68"/>
+      <c r="A160" s="79"/>
+      <c r="B160" s="79"/>
+      <c r="C160" s="79"/>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="68"/>
-      <c r="B161" s="68"/>
-      <c r="C161" s="68"/>
+      <c r="A161" s="14"/>
+      <c r="B161" s="15"/>
+      <c r="C161" s="16"/>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B162" s="76" t="s">
+        <v>257</v>
+      </c>
+      <c r="C162" s="76"/>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B163" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="C163" s="59"/>
+        <v>1</v>
+      </c>
+      <c r="B163" s="77" t="s">
+        <v>258</v>
+      </c>
+      <c r="C163" s="77"/>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B164" s="76" t="s">
+        <v>259</v>
+      </c>
+      <c r="C164" s="76"/>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B165" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C165" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="28.8">
+      <c r="A166" s="111" t="s">
+        <v>260</v>
+      </c>
+      <c r="B166" s="20"/>
+      <c r="C166" s="58" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" s="55"/>
+      <c r="B167" s="20"/>
+      <c r="C167" s="56"/>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B168" s="76" t="s">
+        <v>263</v>
+      </c>
+      <c r="C168" s="76"/>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B164" s="58" t="s">
-        <v>95</v>
-      </c>
-      <c r="C164" s="58"/>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" s="17" t="s">
+      <c r="B169" s="77" t="s">
+        <v>262</v>
+      </c>
+      <c r="C169" s="77"/>
+    </row>
+    <row r="170" spans="1:3" ht="14.4" customHeight="1">
+      <c r="A170" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B165" s="59" t="s">
-        <v>112</v>
-      </c>
-      <c r="C165" s="59"/>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" s="18" t="s">
+      <c r="B170" s="76" t="s">
+        <v>259</v>
+      </c>
+      <c r="C170" s="76"/>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B166" s="18" t="s">
+      <c r="B171" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C166" s="18" t="s">
+      <c r="C171" s="18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
-      <c r="A167" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B167" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C167" s="25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="15" thickBot="1">
-      <c r="A168" s="11"/>
-      <c r="B168" s="29"/>
-      <c r="C168" s="11"/>
-    </row>
-    <row r="169" spans="1:3" ht="15" thickBot="1"/>
-    <row r="170" spans="1:3" ht="15" thickBot="1">
-      <c r="A170" s="2" t="s">
+    <row r="172" spans="1:3" ht="14.4" customHeight="1">
+      <c r="A172" s="55" t="s">
+        <v>265</v>
+      </c>
+      <c r="B172" s="20"/>
+      <c r="C172" s="58" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="14.4" customHeight="1">
+      <c r="A173" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="B173" s="20"/>
+      <c r="C173" s="55" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" s="14"/>
+      <c r="B174" s="15"/>
+      <c r="C174" s="16"/>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B170" s="69" t="s">
-        <v>98</v>
-      </c>
-      <c r="C170" s="70"/>
-    </row>
-    <row r="171" spans="1:3" ht="15" thickBot="1">
-      <c r="A171" s="4" t="s">
+      <c r="B175" s="76" t="s">
+        <v>267</v>
+      </c>
+      <c r="C175" s="76"/>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B171" s="71" t="s">
-        <v>99</v>
-      </c>
-      <c r="C171" s="72"/>
-    </row>
-    <row r="172" spans="1:3" ht="15" thickBot="1">
-      <c r="A172" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B172" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="C172" s="74"/>
-    </row>
-    <row r="173" spans="1:3" ht="15" thickBot="1">
-      <c r="A173" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C173" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" ht="15" thickBot="1">
-      <c r="A174" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B174" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C174" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" ht="15" thickBot="1">
-      <c r="A175" s="3"/>
-      <c r="B175" s="7"/>
-      <c r="C175" s="3"/>
+      <c r="B176" s="77" t="s">
+        <v>271</v>
+      </c>
+      <c r="C176" s="77"/>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B177" s="76" t="s">
+        <v>259</v>
+      </c>
+      <c r="C177" s="76"/>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B178" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C178" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" s="55" t="s">
+        <v>265</v>
+      </c>
+      <c r="B179" s="20"/>
+      <c r="C179" s="58" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" s="55" t="s">
+        <v>268</v>
+      </c>
+      <c r="B180" s="20"/>
+      <c r="C180" s="58" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" s="14"/>
+      <c r="B181" s="15"/>
+      <c r="C181" s="16"/>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B177" s="59" t="s">
-        <v>101</v>
-      </c>
-      <c r="C177" s="59"/>
-    </row>
-    <row r="178" spans="1:3">
-      <c r="A178" s="17" t="s">
+      <c r="B182" s="76" t="s">
+        <v>270</v>
+      </c>
+      <c r="C182" s="76"/>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B178" s="58" t="s">
-        <v>102</v>
-      </c>
-      <c r="C178" s="58"/>
-    </row>
-    <row r="179" spans="1:3">
-      <c r="A179" s="17" t="s">
+      <c r="B183" s="77" t="s">
+        <v>272</v>
+      </c>
+      <c r="C183" s="77"/>
+    </row>
+    <row r="184" spans="1:3" ht="14.4" customHeight="1">
+      <c r="A184" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B179" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="C179" s="59"/>
-    </row>
-    <row r="180" spans="1:3">
-      <c r="A180" s="18" t="s">
+      <c r="B184" s="76" t="s">
+        <v>259</v>
+      </c>
+      <c r="C184" s="76"/>
+    </row>
+    <row r="185" spans="1:3" ht="14.4" customHeight="1">
+      <c r="A185" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B180" s="18" t="s">
+      <c r="B185" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C180" s="18" t="s">
+      <c r="C185" s="18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
-      <c r="A181" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B181" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C181" s="59" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B182" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C182" s="59"/>
-    </row>
-    <row r="185" spans="1:3">
-      <c r="A185" s="17" t="s">
+    <row r="186" spans="1:3">
+      <c r="A186" s="55" t="s">
+        <v>265</v>
+      </c>
+      <c r="B186" s="20"/>
+      <c r="C186" s="58" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="B187" s="20"/>
+      <c r="C187" s="55" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="14.4" customHeight="1">
+      <c r="A188" s="55"/>
+      <c r="B188" s="20"/>
+      <c r="C188" s="55"/>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189" s="14"/>
+      <c r="B189" s="15"/>
+      <c r="C189" s="16"/>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B185" s="59" t="s">
-        <v>106</v>
-      </c>
-      <c r="C185" s="59"/>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="A186" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B186" s="58" t="s">
-        <v>107</v>
-      </c>
-      <c r="C186" s="58"/>
-    </row>
-    <row r="187" spans="1:3">
-      <c r="A187" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B187" s="59" t="s">
-        <v>108</v>
-      </c>
-      <c r="C187" s="59"/>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="A188" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B188" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C188" s="18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3">
-      <c r="A189" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="B189" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C189" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3">
-      <c r="A190" s="10"/>
-      <c r="B190" s="30"/>
-      <c r="C190" s="13"/>
+      <c r="B190" s="76" t="s">
+        <v>275</v>
+      </c>
+      <c r="C190" s="76"/>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B191" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="C191" s="59"/>
+        <v>1</v>
+      </c>
+      <c r="B191" s="77" t="s">
+        <v>276</v>
+      </c>
+      <c r="C191" s="77"/>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B192" s="76" t="s">
+        <v>277</v>
+      </c>
+      <c r="C192" s="76"/>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B193" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C193" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" s="55" t="s">
+        <v>265</v>
+      </c>
+      <c r="B194" s="20"/>
+      <c r="C194" s="58" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="B195" s="20"/>
+      <c r="C195" s="55" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" s="14"/>
+      <c r="B196" s="15"/>
+      <c r="C196" s="16"/>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B197" s="76" t="s">
+        <v>280</v>
+      </c>
+      <c r="C197" s="76"/>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B192" s="58" t="s">
-        <v>114</v>
-      </c>
-      <c r="C192" s="58"/>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193" s="17" t="s">
+      <c r="B198" s="77" t="s">
+        <v>279</v>
+      </c>
+      <c r="C198" s="77"/>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B193" s="59" t="s">
-        <v>113</v>
-      </c>
-      <c r="C193" s="59"/>
-    </row>
-    <row r="194" spans="1:3">
-      <c r="A194" s="18" t="s">
+      <c r="B199" s="76" t="s">
+        <v>281</v>
+      </c>
+      <c r="C199" s="76"/>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B194" s="18" t="s">
+      <c r="B200" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C194" s="18" t="s">
+      <c r="C200" s="18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:3">
-      <c r="A195" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B195" s="20" t="s">
+    <row r="201" spans="1:3">
+      <c r="A201" s="55" t="s">
+        <v>282</v>
+      </c>
+      <c r="B201" s="20"/>
+      <c r="C201" s="58" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" s="14"/>
+      <c r="B202" s="15"/>
+      <c r="C202" s="16"/>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B203" s="76" t="s">
+        <v>285</v>
+      </c>
+      <c r="C203" s="76"/>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B204" s="77" t="s">
+        <v>284</v>
+      </c>
+      <c r="C204" s="77"/>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B205" s="76" t="s">
+        <v>277</v>
+      </c>
+      <c r="C205" s="76"/>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B206" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C206" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
+      <c r="A207" s="55" t="s">
+        <v>265</v>
+      </c>
+      <c r="B207" s="20"/>
+      <c r="C207" s="58" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" s="55" t="s">
+        <v>288</v>
+      </c>
+      <c r="B208" s="20"/>
+      <c r="C208" s="58" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3">
+      <c r="A209" s="14"/>
+      <c r="B209" s="15"/>
+      <c r="C209" s="14"/>
+    </row>
+    <row r="210" spans="1:3">
+      <c r="A210" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B210" s="76" t="s">
+        <v>286</v>
+      </c>
+      <c r="C210" s="76"/>
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B211" s="77" t="s">
+        <v>290</v>
+      </c>
+      <c r="C211" s="77"/>
+    </row>
+    <row r="212" spans="1:3">
+      <c r="A212" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B212" s="76" t="s">
+        <v>291</v>
+      </c>
+      <c r="C212" s="76"/>
+    </row>
+    <row r="213" spans="1:3">
+      <c r="A213" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B213" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C213" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="27">
+      <c r="A214" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="B214" s="20"/>
+      <c r="C214" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3">
+      <c r="A215" s="55" t="s">
+        <v>294</v>
+      </c>
+      <c r="B215" s="20"/>
+      <c r="C215" s="55" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3">
+      <c r="A216" s="14"/>
+      <c r="B216" s="15"/>
+      <c r="C216" s="16"/>
+    </row>
+    <row r="218" spans="1:3">
+      <c r="A218" s="103" t="s">
+        <v>169</v>
+      </c>
+      <c r="B218" s="104"/>
+      <c r="C218" s="105"/>
+    </row>
+    <row r="219" spans="1:3">
+      <c r="A219" s="106"/>
+      <c r="B219" s="107"/>
+      <c r="C219" s="108"/>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B221" s="101" t="s">
+        <v>94</v>
+      </c>
+      <c r="C221" s="102"/>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B222" s="109" t="s">
+        <v>95</v>
+      </c>
+      <c r="C222" s="110"/>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B223" s="76" t="s">
+        <v>112</v>
+      </c>
+      <c r="C223" s="76"/>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B224" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C224" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B225" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C195" s="19" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" ht="15" thickBot="1"/>
-    <row r="197" spans="1:3">
-      <c r="A197" s="62" t="s">
-        <v>170</v>
-      </c>
-      <c r="B197" s="63"/>
-      <c r="C197" s="64"/>
-    </row>
-    <row r="198" spans="1:3" ht="15" thickBot="1">
-      <c r="A198" s="65"/>
-      <c r="B198" s="66"/>
-      <c r="C198" s="67"/>
-    </row>
-    <row r="200" spans="1:3">
-      <c r="A200" s="17" t="s">
+      <c r="C225" s="25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="15" thickBot="1">
+      <c r="A226" s="11"/>
+      <c r="B226" s="29"/>
+      <c r="C226" s="11"/>
+    </row>
+    <row r="227" spans="1:4" ht="15" thickBot="1"/>
+    <row r="228" spans="1:4" ht="15" thickBot="1">
+      <c r="A228" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B200" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="C200" s="59"/>
-    </row>
-    <row r="201" spans="1:3">
-      <c r="A201" s="17" t="s">
+      <c r="B228" s="89" t="s">
+        <v>98</v>
+      </c>
+      <c r="C228" s="90"/>
+    </row>
+    <row r="229" spans="1:4" ht="15" thickBot="1">
+      <c r="A229" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B201" s="58" t="s">
-        <v>123</v>
-      </c>
-      <c r="C201" s="58"/>
-    </row>
-    <row r="202" spans="1:3">
-      <c r="A202" s="17" t="s">
+      <c r="B229" s="85" t="s">
+        <v>99</v>
+      </c>
+      <c r="C229" s="86"/>
+    </row>
+    <row r="230" spans="1:4" ht="15" thickBot="1">
+      <c r="A230" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B202" s="59" t="s">
-        <v>133</v>
-      </c>
-      <c r="C202" s="59"/>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="A203" s="18" t="s">
+      <c r="B230" s="87" t="s">
+        <v>112</v>
+      </c>
+      <c r="C230" s="88"/>
+      <c r="D230" s="43" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="15" thickBot="1">
+      <c r="A231" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B203" s="18" t="s">
+      <c r="B231" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C203" s="18" t="s">
+      <c r="C231" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:3">
-      <c r="A204" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="B204" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="C204" s="26" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3">
-      <c r="A205" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="B205" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C205" s="26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3">
-      <c r="A206" s="94" t="s">
-        <v>126</v>
-      </c>
-      <c r="B206" s="95">
-        <v>18000</v>
-      </c>
-      <c r="C206" s="96" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3">
-      <c r="A207" s="94" t="s">
-        <v>136</v>
-      </c>
-      <c r="B207" s="94"/>
-      <c r="C207" s="96" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4">
-      <c r="A209" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B209" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="C209" s="59"/>
-    </row>
-    <row r="210" spans="1:4">
-      <c r="A210" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B210" s="58" t="s">
-        <v>134</v>
-      </c>
-      <c r="C210" s="58"/>
-    </row>
-    <row r="211" spans="1:4">
-      <c r="A211" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B211" s="59" t="s">
-        <v>133</v>
-      </c>
-      <c r="C211" s="59"/>
-    </row>
-    <row r="212" spans="1:4">
-      <c r="A212" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B212" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C212" s="18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4">
-      <c r="A213" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="B213" s="20"/>
-      <c r="C213" s="31" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4">
-      <c r="A214" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="B214" s="20"/>
-      <c r="C214" s="19" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4">
-      <c r="A217" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B217" s="59" t="s">
-        <v>120</v>
-      </c>
-      <c r="C217" s="59"/>
-    </row>
-    <row r="218" spans="1:4">
-      <c r="A218" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B218" s="58" t="s">
-        <v>140</v>
-      </c>
-      <c r="C218" s="58"/>
-    </row>
-    <row r="219" spans="1:4">
-      <c r="A219" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B219" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="C219" s="59"/>
-    </row>
-    <row r="220" spans="1:4">
-      <c r="A220" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B220" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C220" s="18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4">
-      <c r="A221" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="B221" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="C221" s="26" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4">
-      <c r="A222" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="B222" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C222" s="26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4">
-      <c r="A223" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="B223" s="41">
-        <v>18000</v>
-      </c>
-      <c r="C223" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="D223" s="43" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4">
-      <c r="A224" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="B224" s="27"/>
-      <c r="C224" s="42" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3">
-      <c r="A226" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="B226" s="76" t="s">
-        <v>121</v>
-      </c>
-      <c r="C226" s="76"/>
-    </row>
-    <row r="227" spans="1:3">
-      <c r="A227" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="B227" s="75" t="s">
-        <v>142</v>
-      </c>
-      <c r="C227" s="75"/>
-    </row>
-    <row r="228" spans="1:3">
-      <c r="A228" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="B228" s="76" t="s">
-        <v>133</v>
-      </c>
-      <c r="C228" s="76"/>
-    </row>
-    <row r="229" spans="1:3">
-      <c r="A229" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B229" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="C229" s="33" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3">
-      <c r="A230" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="B230" s="34"/>
-      <c r="C230" s="35" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3">
-      <c r="A231" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="B231" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="C231" s="35" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3">
-      <c r="A232" s="44" t="s">
-        <v>126</v>
-      </c>
-      <c r="B232" s="45">
-        <v>18000</v>
-      </c>
-      <c r="C232" s="46" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3">
-      <c r="A233" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="B233" s="44"/>
-      <c r="C233" s="46" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3">
+    <row r="232" spans="1:4" ht="15" thickBot="1">
+      <c r="A232" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="15" thickBot="1">
+      <c r="A233" s="3"/>
+      <c r="B233" s="7"/>
+      <c r="C233" s="3"/>
+    </row>
+    <row r="235" spans="1:4">
       <c r="A235" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B235" s="59" t="s">
-        <v>122</v>
-      </c>
-      <c r="C235" s="59"/>
-    </row>
-    <row r="236" spans="1:3">
+      <c r="B235" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="C235" s="76"/>
+    </row>
+    <row r="236" spans="1:4">
       <c r="A236" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B236" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="C236" s="58"/>
-    </row>
-    <row r="237" spans="1:3">
+      <c r="B236" s="77" t="s">
+        <v>102</v>
+      </c>
+      <c r="C236" s="77"/>
+    </row>
+    <row r="237" spans="1:4">
       <c r="A237" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B237" s="59" t="s">
-        <v>133</v>
-      </c>
-      <c r="C237" s="59"/>
-    </row>
-    <row r="238" spans="1:3">
+      <c r="B237" s="76" t="s">
+        <v>103</v>
+      </c>
+      <c r="C237" s="76"/>
+    </row>
+    <row r="238" spans="1:4">
       <c r="A238" s="18" t="s">
         <v>2</v>
       </c>
@@ -4234,866 +4691,1304 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:3">
+    <row r="239" spans="1:4">
       <c r="A239" s="19" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="B239" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="C239" s="26" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
+        <v>14</v>
+      </c>
+      <c r="C239" s="76" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
       <c r="A240" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B240" s="20"/>
-      <c r="C240" s="26" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="B241" s="41">
-        <v>18000</v>
-      </c>
-      <c r="C241" s="42" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="A242" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="B242" s="27"/>
-      <c r="C242" s="42" t="s">
-        <v>141</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="B240" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C240" s="76"/>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B243" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="C243" s="76"/>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B244" s="59" t="s">
-        <v>143</v>
-      </c>
-      <c r="C244" s="59"/>
+        <v>1</v>
+      </c>
+      <c r="B244" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="C244" s="77"/>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B245" s="76" t="s">
+        <v>108</v>
+      </c>
+      <c r="C245" s="76"/>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B246" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C246" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B247" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C247" s="19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" s="10"/>
+      <c r="B248" s="30"/>
+      <c r="C248" s="13"/>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B249" s="76" t="s">
+        <v>111</v>
+      </c>
+      <c r="C249" s="76"/>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B245" s="58" t="s">
+      <c r="B250" s="77" t="s">
+        <v>114</v>
+      </c>
+      <c r="C250" s="77"/>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B251" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="C251" s="76"/>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B252" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C252" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B253" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C253" s="19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="15" thickBot="1"/>
+    <row r="255" spans="1:3">
+      <c r="A255" s="70" t="s">
+        <v>170</v>
+      </c>
+      <c r="B255" s="71"/>
+      <c r="C255" s="72"/>
+    </row>
+    <row r="256" spans="1:3" ht="15" thickBot="1">
+      <c r="A256" s="73"/>
+      <c r="B256" s="74"/>
+      <c r="C256" s="75"/>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B258" s="83" t="s">
+        <v>117</v>
+      </c>
+      <c r="C258" s="83"/>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B259" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="C259" s="77"/>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B260" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="C260" s="76"/>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B261" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C261" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E261" s="67" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B262" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C262" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="E262" s="68"/>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B263" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C263" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="E263" s="68"/>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="B264" s="65">
+        <v>18000</v>
+      </c>
+      <c r="C264" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="E264" s="68"/>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="B265" s="64"/>
+      <c r="C265" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="E265" s="68"/>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="E266" s="68"/>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B267" s="83" t="s">
+        <v>119</v>
+      </c>
+      <c r="C267" s="83"/>
+      <c r="E267" s="68"/>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B268" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="C268" s="77"/>
+      <c r="E268" s="69"/>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B269" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="C269" s="76"/>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B270" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C270" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B271" s="20"/>
+      <c r="C271" s="31" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B272" s="20"/>
+      <c r="C272" s="19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B275" s="83" t="s">
+        <v>120</v>
+      </c>
+      <c r="C275" s="83"/>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B276" s="77" t="s">
+        <v>140</v>
+      </c>
+      <c r="C276" s="77"/>
+    </row>
+    <row r="277" spans="1:3">
+      <c r="A277" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B277" s="76" t="s">
+        <v>139</v>
+      </c>
+      <c r="C277" s="76"/>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B278" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C278" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B279" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C279" s="26" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B280" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C280" s="26" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="B281" s="65">
+        <v>18000</v>
+      </c>
+      <c r="C281" s="66" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="B282" s="64"/>
+      <c r="C282" s="66" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="A284" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B284" s="84" t="s">
+        <v>121</v>
+      </c>
+      <c r="C284" s="84"/>
+    </row>
+    <row r="285" spans="1:3">
+      <c r="A285" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B285" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="C285" s="81"/>
+    </row>
+    <row r="286" spans="1:3">
+      <c r="A286" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B286" s="82" t="s">
+        <v>133</v>
+      </c>
+      <c r="C286" s="82"/>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B287" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C287" s="33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="B288" s="34"/>
+      <c r="C288" s="35" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="B289" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C289" s="35" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="B290" s="45">
+        <v>18000</v>
+      </c>
+      <c r="C290" s="46" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="B291" s="44"/>
+      <c r="C291" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="E291" s="67" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="E292" s="68"/>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B293" s="76" t="s">
+        <v>122</v>
+      </c>
+      <c r="C293" s="76"/>
+      <c r="E293" s="68"/>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B294" s="77" t="s">
+        <v>145</v>
+      </c>
+      <c r="C294" s="77"/>
+      <c r="E294" s="68"/>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B295" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="C295" s="76"/>
+      <c r="D295" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="E295" s="68"/>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B296" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C296" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E296" s="68"/>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B297" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C297" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="E297" s="68"/>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B298" s="20"/>
+      <c r="C298" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="E298" s="69"/>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="B299" s="41">
+        <v>18000</v>
+      </c>
+      <c r="C299" s="42" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B300" s="27"/>
+      <c r="C300" s="42" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B302" s="76" t="s">
+        <v>143</v>
+      </c>
+      <c r="C302" s="76"/>
+      <c r="E302" s="67" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B303" s="77" t="s">
         <v>144</v>
       </c>
-      <c r="C245" s="58"/>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246" s="17" t="s">
+      <c r="C303" s="77"/>
+      <c r="E303" s="68"/>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B246" s="59" t="s">
+      <c r="B304" s="76" t="s">
         <v>133</v>
       </c>
-      <c r="C246" s="59"/>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247" s="18" t="s">
+      <c r="C304" s="76"/>
+      <c r="E304" s="68"/>
+    </row>
+    <row r="305" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A305" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B247" s="18" t="s">
+      <c r="B305" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C247" s="18" t="s">
+      <c r="C305" s="18" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="248" spans="1:3">
-      <c r="A248" s="19" t="s">
+      <c r="E305" s="68"/>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="B248" s="20" t="s">
+      <c r="B306" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C248" s="26" t="s">
+      <c r="C306" s="26" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249" s="19" t="s">
+      <c r="E306" s="68"/>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="B249" s="20" t="s">
+      <c r="B307" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C249" s="26" t="s">
+      <c r="C307" s="26" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="250" spans="1:3">
-      <c r="A250" s="94" t="s">
+      <c r="E307" s="68"/>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="64" t="s">
         <v>148</v>
       </c>
-      <c r="B250" s="95"/>
-      <c r="C250" s="40" t="s">
+      <c r="B308" s="65"/>
+      <c r="C308" s="40" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="251" spans="1:3">
-      <c r="A251" s="94" t="s">
+      <c r="E308" s="68"/>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="B251" s="94"/>
-      <c r="C251" s="96" t="s">
+      <c r="B309" s="64"/>
+      <c r="C309" s="66" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="253" spans="1:3">
-      <c r="A253" s="68" t="s">
+      <c r="E309" s="69"/>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="79" t="s">
         <v>171</v>
       </c>
-      <c r="B253" s="68"/>
-      <c r="C253" s="68"/>
-    </row>
-    <row r="254" spans="1:3">
-      <c r="A254" s="68"/>
-      <c r="B254" s="68"/>
-      <c r="C254" s="68"/>
-    </row>
-    <row r="256" spans="1:3">
-      <c r="A256" s="17" t="s">
+      <c r="B311" s="79"/>
+      <c r="C311" s="79"/>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="79"/>
+      <c r="B312" s="79"/>
+      <c r="C312" s="79"/>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="E313" s="67" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B256" s="59" t="s">
+      <c r="B314" s="76" t="s">
         <v>150</v>
       </c>
-      <c r="C256" s="59"/>
-    </row>
-    <row r="257" spans="1:3">
-      <c r="A257" s="17" t="s">
+      <c r="C314" s="76"/>
+      <c r="E314" s="68"/>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B257" s="58" t="s">
+      <c r="B315" s="77" t="s">
         <v>155</v>
       </c>
-      <c r="C257" s="58"/>
-    </row>
-    <row r="258" spans="1:3">
-      <c r="A258" s="17" t="s">
+      <c r="C315" s="77"/>
+      <c r="E315" s="68"/>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B258" s="59" t="s">
+      <c r="B316" s="76" t="s">
         <v>151</v>
       </c>
-      <c r="C258" s="59"/>
-    </row>
-    <row r="259" spans="1:3">
-      <c r="A259" s="18" t="s">
+      <c r="C316" s="76"/>
+      <c r="E316" s="68"/>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B259" s="18" t="s">
+      <c r="B317" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C259" s="18" t="s">
+      <c r="C317" s="18" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="260" spans="1:3">
-      <c r="A260" s="19" t="s">
+      <c r="E317" s="68"/>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="B260" s="20"/>
-      <c r="C260" s="26" t="s">
+      <c r="B318" s="20"/>
+      <c r="C318" s="26" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="261" spans="1:3">
-      <c r="A261" s="19" t="s">
+      <c r="E318" s="68"/>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="B261" s="20"/>
-      <c r="C261" s="26" t="s">
+      <c r="B319" s="20"/>
+      <c r="C319" s="26" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="262" spans="1:3">
-      <c r="A262" s="14"/>
-      <c r="B262" s="15"/>
-      <c r="C262" s="24"/>
-    </row>
-    <row r="263" spans="1:3">
-      <c r="A263" s="47"/>
-      <c r="B263" s="48"/>
-      <c r="C263" s="24"/>
-    </row>
-    <row r="264" spans="1:3">
-      <c r="A264" s="17" t="s">
+      <c r="E319" s="68"/>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="14"/>
+      <c r="B320" s="15"/>
+      <c r="C320" s="24"/>
+      <c r="E320" s="69"/>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="47"/>
+      <c r="B321" s="48"/>
+      <c r="C321" s="24"/>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B264" s="59" t="s">
+      <c r="B322" s="76" t="s">
         <v>157</v>
       </c>
-      <c r="C264" s="59"/>
-    </row>
-    <row r="265" spans="1:3">
-      <c r="A265" s="17" t="s">
+      <c r="C322" s="76"/>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B265" s="58" t="s">
+      <c r="B323" s="77" t="s">
         <v>158</v>
       </c>
-      <c r="C265" s="58"/>
-    </row>
-    <row r="266" spans="1:3">
-      <c r="A266" s="17" t="s">
+      <c r="C323" s="77"/>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B266" s="59" t="s">
+      <c r="B324" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="C266" s="59"/>
-    </row>
-    <row r="267" spans="1:3">
-      <c r="A267" s="18" t="s">
+      <c r="C324" s="76"/>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B267" s="18" t="s">
+      <c r="B325" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C267" s="18" t="s">
+      <c r="C325" s="18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:3">
-      <c r="A268" s="19" t="s">
+    <row r="326" spans="1:5">
+      <c r="A326" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="B268" s="20"/>
-      <c r="C268" s="26" t="s">
+      <c r="B326" s="20"/>
+      <c r="C326" s="26" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="269" spans="1:3">
-      <c r="A269" s="14"/>
-      <c r="B269" s="15"/>
-      <c r="C269" s="24"/>
-    </row>
-    <row r="270" spans="1:3">
-      <c r="A270" s="49"/>
-      <c r="B270" s="49"/>
-      <c r="C270" s="49"/>
-    </row>
-    <row r="271" spans="1:3">
-      <c r="A271" s="17" t="s">
+    <row r="327" spans="1:5">
+      <c r="A327" s="14"/>
+      <c r="B327" s="15"/>
+      <c r="C327" s="24"/>
+      <c r="E327" s="67" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="49"/>
+      <c r="B328" s="49"/>
+      <c r="C328" s="49"/>
+      <c r="E328" s="68"/>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B271" s="59" t="s">
+      <c r="B329" s="76" t="s">
         <v>157</v>
       </c>
-      <c r="C271" s="59"/>
-    </row>
-    <row r="272" spans="1:3">
-      <c r="A272" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B272" s="58" t="s">
-        <v>162</v>
-      </c>
-      <c r="C272" s="58"/>
-    </row>
-    <row r="273" spans="1:4">
-      <c r="A273" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B273" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="C273" s="59"/>
-    </row>
-    <row r="274" spans="1:4">
-      <c r="A274" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B274" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C274" s="18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4">
-      <c r="A275" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="B275" s="20"/>
-      <c r="C275" s="77" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4">
-      <c r="A276" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="B276" s="27"/>
-      <c r="C276" s="77"/>
-    </row>
-    <row r="277" spans="1:4">
-      <c r="A277" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="B277" s="27"/>
-      <c r="C277" s="77"/>
-    </row>
-    <row r="279" spans="1:4">
-      <c r="A279" s="68" t="s">
-        <v>228</v>
-      </c>
-      <c r="B279" s="68"/>
-      <c r="C279" s="68"/>
-    </row>
-    <row r="280" spans="1:4">
-      <c r="A280" s="68"/>
-      <c r="B280" s="68"/>
-      <c r="C280" s="68"/>
-    </row>
-    <row r="282" spans="1:4">
-      <c r="A282" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B282" s="59" t="s">
-        <v>227</v>
-      </c>
-      <c r="C282" s="59"/>
-    </row>
-    <row r="283" spans="1:4">
-      <c r="A283" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B283" s="58" t="s">
-        <v>173</v>
-      </c>
-      <c r="C283" s="58"/>
-    </row>
-    <row r="284" spans="1:4">
-      <c r="A284" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B284" s="59" t="s">
-        <v>174</v>
-      </c>
-      <c r="C284" s="59"/>
-    </row>
-    <row r="285" spans="1:4">
-      <c r="A285" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B285" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C285" s="18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4">
-      <c r="A286" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="B286" s="20"/>
-      <c r="C286" s="26" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" ht="27">
-      <c r="A287" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B287" s="20"/>
-      <c r="C287" s="26" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4">
-      <c r="A288" s="87" t="s">
-        <v>177</v>
-      </c>
-      <c r="B288" s="20"/>
-      <c r="C288" s="50" t="s">
-        <v>197</v>
-      </c>
-      <c r="D288" s="43" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3">
-      <c r="A289" s="19"/>
-      <c r="B289" s="20"/>
-      <c r="C289" s="26"/>
-    </row>
-    <row r="290" spans="1:3" ht="15" thickBot="1">
-      <c r="A290" s="21"/>
-      <c r="B290" s="22"/>
-      <c r="C290" s="23"/>
-    </row>
-    <row r="291" spans="1:3">
-      <c r="A291" s="62" t="s">
-        <v>184</v>
-      </c>
-      <c r="B291" s="63"/>
-      <c r="C291" s="64"/>
-    </row>
-    <row r="292" spans="1:3" ht="15" thickBot="1">
-      <c r="A292" s="65"/>
-      <c r="B292" s="66"/>
-      <c r="C292" s="67"/>
-    </row>
-    <row r="294" spans="1:3">
-      <c r="A294" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B294" s="59" t="s">
-        <v>185</v>
-      </c>
-      <c r="C294" s="59"/>
-    </row>
-    <row r="295" spans="1:3">
-      <c r="A295" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B295" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="C295" s="58"/>
-    </row>
-    <row r="296" spans="1:3">
-      <c r="A296" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B296" s="59" t="s">
-        <v>174</v>
-      </c>
-      <c r="C296" s="59"/>
-    </row>
-    <row r="297" spans="1:3">
-      <c r="A297" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B297" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C297" s="18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A298" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="B298" s="20"/>
-      <c r="C298" s="78" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3">
-      <c r="A299" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="B299" s="20"/>
-      <c r="C299" s="78"/>
-    </row>
-    <row r="300" spans="1:3">
-      <c r="A300" s="19"/>
-      <c r="B300" s="20"/>
-      <c r="C300" s="78"/>
-    </row>
-    <row r="301" spans="1:3">
-      <c r="A301" s="27"/>
-      <c r="B301" s="27"/>
-      <c r="C301" s="78"/>
-    </row>
-    <row r="302" spans="1:3" ht="15" thickBot="1"/>
-    <row r="303" spans="1:3">
-      <c r="A303" s="62" t="s">
-        <v>225</v>
-      </c>
-      <c r="B303" s="63"/>
-      <c r="C303" s="64"/>
-    </row>
-    <row r="304" spans="1:3" ht="15" thickBot="1">
-      <c r="A304" s="65"/>
-      <c r="B304" s="66"/>
-      <c r="C304" s="67"/>
-    </row>
-    <row r="306" spans="1:3">
-      <c r="A306" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B306" s="59" t="s">
-        <v>226</v>
-      </c>
-      <c r="C306" s="59"/>
-    </row>
-    <row r="307" spans="1:3">
-      <c r="A307" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B307" s="58" t="s">
-        <v>229</v>
-      </c>
-      <c r="C307" s="58"/>
-    </row>
-    <row r="308" spans="1:3">
-      <c r="A308" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B308" s="59" t="s">
-        <v>230</v>
-      </c>
-      <c r="C308" s="59"/>
-    </row>
-    <row r="309" spans="1:3">
-      <c r="A309" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B309" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C309" s="18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3">
-      <c r="A310" s="88" t="s">
-        <v>231</v>
-      </c>
-      <c r="B310" s="20"/>
-      <c r="C310" s="88" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" ht="52.8">
-      <c r="A311" s="89" t="s">
-        <v>232</v>
-      </c>
-      <c r="B311" s="90" t="s">
-        <v>239</v>
-      </c>
-      <c r="C311" s="89" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3">
-      <c r="A312" s="88" t="s">
-        <v>233</v>
-      </c>
-      <c r="B312" s="20"/>
-      <c r="C312" s="88" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3">
-      <c r="A313" s="88" t="s">
-        <v>234</v>
-      </c>
-      <c r="B313" s="27"/>
-      <c r="C313" s="88" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" ht="15" thickBot="1"/>
-    <row r="315" spans="1:3">
-      <c r="A315" s="62" t="s">
-        <v>240</v>
-      </c>
-      <c r="B315" s="63"/>
-      <c r="C315" s="64"/>
-    </row>
-    <row r="316" spans="1:3" ht="15" thickBot="1">
-      <c r="A316" s="65"/>
-      <c r="B316" s="66"/>
-      <c r="C316" s="67"/>
-    </row>
-    <row r="318" spans="1:3">
-      <c r="A318" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B318" s="59" t="s">
-        <v>172</v>
-      </c>
-      <c r="C318" s="59"/>
-    </row>
-    <row r="319" spans="1:3">
-      <c r="A319" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B319" s="58" t="s">
-        <v>241</v>
-      </c>
-      <c r="C319" s="58"/>
-    </row>
-    <row r="320" spans="1:3">
-      <c r="A320" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B320" s="59" t="s">
-        <v>242</v>
-      </c>
-      <c r="C320" s="59"/>
-    </row>
-    <row r="321" spans="1:5">
-      <c r="A321" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B321" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C321" s="18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5" ht="15">
-      <c r="A322" t="s">
-        <v>243</v>
-      </c>
-      <c r="B322" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="C322" s="88" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5">
-      <c r="A323" t="s">
-        <v>246</v>
-      </c>
-      <c r="B323" s="90" t="s">
-        <v>17</v>
-      </c>
-      <c r="C323" s="88" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5">
-      <c r="A324" s="88" t="s">
-        <v>233</v>
-      </c>
-      <c r="B324" s="20"/>
-      <c r="C324" s="88" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5" ht="15" thickBot="1"/>
-    <row r="327" spans="1:5">
-      <c r="A327" s="62" t="s">
-        <v>248</v>
-      </c>
-      <c r="B327" s="63"/>
-      <c r="C327" s="64"/>
-    </row>
-    <row r="328" spans="1:5" ht="15" thickBot="1">
-      <c r="A328" s="65"/>
-      <c r="B328" s="66"/>
-      <c r="C328" s="67"/>
-    </row>
-    <row r="329" spans="1:5">
-      <c r="E329" s="55" t="s">
-        <v>218</v>
-      </c>
+      <c r="C329" s="76"/>
+      <c r="E329" s="68"/>
     </row>
     <row r="330" spans="1:5">
       <c r="A330" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B330" s="59" t="s">
-        <v>249</v>
-      </c>
-      <c r="C330" s="59"/>
-      <c r="E330" s="56"/>
+        <v>1</v>
+      </c>
+      <c r="B330" s="77" t="s">
+        <v>162</v>
+      </c>
+      <c r="C330" s="77"/>
+      <c r="E330" s="68"/>
     </row>
     <row r="331" spans="1:5">
       <c r="A331" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B331" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="C331" s="76"/>
+      <c r="E331" s="68"/>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B332" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C332" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E332" s="68"/>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B333" s="20"/>
+      <c r="C333" s="80" t="s">
+        <v>166</v>
+      </c>
+      <c r="E333" s="68"/>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B334" s="27"/>
+      <c r="C334" s="80"/>
+      <c r="E334" s="69"/>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B335" s="27"/>
+      <c r="C335" s="80"/>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="E336" s="67" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="79" t="s">
+        <v>228</v>
+      </c>
+      <c r="B337" s="79"/>
+      <c r="C337" s="79"/>
+      <c r="E337" s="68"/>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="79"/>
+      <c r="B338" s="79"/>
+      <c r="C338" s="79"/>
+      <c r="E338" s="68"/>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="E339" s="68"/>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B340" s="76" t="s">
+        <v>227</v>
+      </c>
+      <c r="C340" s="76"/>
+      <c r="E340" s="68"/>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B331" s="58" t="s">
+      <c r="B341" s="77" t="s">
+        <v>173</v>
+      </c>
+      <c r="C341" s="77"/>
+      <c r="E341" s="68"/>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B342" s="76" t="s">
+        <v>174</v>
+      </c>
+      <c r="C342" s="76"/>
+      <c r="E342" s="68"/>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B343" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C343" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E343" s="69"/>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="B344" s="20"/>
+      <c r="C344" s="26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" ht="27">
+      <c r="A345" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B345" s="20"/>
+      <c r="C345" s="26" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="57" t="s">
+        <v>177</v>
+      </c>
+      <c r="B346" s="20"/>
+      <c r="C346" s="50" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="19"/>
+      <c r="B347" s="20"/>
+      <c r="C347" s="26"/>
+    </row>
+    <row r="348" spans="1:5" ht="15" thickBot="1">
+      <c r="A348" s="21"/>
+      <c r="B348" s="22"/>
+      <c r="C348" s="23"/>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="70" t="s">
+        <v>184</v>
+      </c>
+      <c r="B349" s="71"/>
+      <c r="C349" s="72"/>
+    </row>
+    <row r="350" spans="1:5" ht="15" thickBot="1">
+      <c r="A350" s="73"/>
+      <c r="B350" s="74"/>
+      <c r="C350" s="75"/>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B352" s="76" t="s">
+        <v>185</v>
+      </c>
+      <c r="C352" s="76"/>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B353" s="77" t="s">
+        <v>188</v>
+      </c>
+      <c r="C353" s="77"/>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B354" s="76" t="s">
+        <v>174</v>
+      </c>
+      <c r="C354" s="76"/>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B355" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C355" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="B356" s="20"/>
+      <c r="C356" s="78" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="B357" s="20"/>
+      <c r="C357" s="78"/>
+    </row>
+    <row r="358" spans="1:3">
+      <c r="A358" s="19"/>
+      <c r="B358" s="20"/>
+      <c r="C358" s="78"/>
+    </row>
+    <row r="359" spans="1:3">
+      <c r="A359" s="27"/>
+      <c r="B359" s="27"/>
+      <c r="C359" s="78"/>
+    </row>
+    <row r="360" spans="1:3" ht="15" thickBot="1"/>
+    <row r="361" spans="1:3">
+      <c r="A361" s="70" t="s">
+        <v>225</v>
+      </c>
+      <c r="B361" s="71"/>
+      <c r="C361" s="72"/>
+    </row>
+    <row r="362" spans="1:3" ht="15" thickBot="1">
+      <c r="A362" s="73"/>
+      <c r="B362" s="74"/>
+      <c r="C362" s="75"/>
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B364" s="76" t="s">
+        <v>226</v>
+      </c>
+      <c r="C364" s="76"/>
+    </row>
+    <row r="365" spans="1:3">
+      <c r="A365" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B365" s="77" t="s">
+        <v>229</v>
+      </c>
+      <c r="C365" s="77"/>
+    </row>
+    <row r="366" spans="1:3">
+      <c r="A366" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B366" s="76" t="s">
+        <v>230</v>
+      </c>
+      <c r="C366" s="76"/>
+    </row>
+    <row r="367" spans="1:3">
+      <c r="A367" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B367" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C367" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3">
+      <c r="A368" s="58" t="s">
+        <v>231</v>
+      </c>
+      <c r="B368" s="20"/>
+      <c r="C368" s="58" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" ht="52.8">
+      <c r="A369" s="59" t="s">
+        <v>232</v>
+      </c>
+      <c r="B369" s="60" t="s">
+        <v>239</v>
+      </c>
+      <c r="C369" s="59" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3">
+      <c r="A370" s="58" t="s">
+        <v>233</v>
+      </c>
+      <c r="B370" s="20"/>
+      <c r="C370" s="58" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3">
+      <c r="A371" s="58" t="s">
+        <v>234</v>
+      </c>
+      <c r="B371" s="27"/>
+      <c r="C371" s="58" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" ht="15" thickBot="1"/>
+    <row r="373" spans="1:3">
+      <c r="A373" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="B373" s="71"/>
+      <c r="C373" s="72"/>
+    </row>
+    <row r="374" spans="1:3" ht="15" thickBot="1">
+      <c r="A374" s="73"/>
+      <c r="B374" s="74"/>
+      <c r="C374" s="75"/>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B376" s="76" t="s">
+        <v>172</v>
+      </c>
+      <c r="C376" s="76"/>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B377" s="77" t="s">
+        <v>241</v>
+      </c>
+      <c r="C377" s="77"/>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B378" s="76" t="s">
+        <v>242</v>
+      </c>
+      <c r="C378" s="76"/>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B379" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C379" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" ht="15">
+      <c r="A380" t="s">
+        <v>243</v>
+      </c>
+      <c r="B380" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="C380" s="58" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3">
+      <c r="A381" t="s">
+        <v>246</v>
+      </c>
+      <c r="B381" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="C381" s="58" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382" s="58" t="s">
+        <v>233</v>
+      </c>
+      <c r="B382" s="20"/>
+      <c r="C382" s="58" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" ht="15" thickBot="1"/>
+    <row r="385" spans="1:3">
+      <c r="A385" s="70" t="s">
+        <v>248</v>
+      </c>
+      <c r="B385" s="71"/>
+      <c r="C385" s="72"/>
+    </row>
+    <row r="386" spans="1:3" ht="15" thickBot="1">
+      <c r="A386" s="73"/>
+      <c r="B386" s="74"/>
+      <c r="C386" s="75"/>
+    </row>
+    <row r="388" spans="1:3">
+      <c r="A388" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B388" s="76" t="s">
+        <v>249</v>
+      </c>
+      <c r="C388" s="76"/>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B389" s="77" t="s">
         <v>250</v>
       </c>
-      <c r="C331" s="58"/>
-      <c r="E331" s="56"/>
-    </row>
-    <row r="332" spans="1:5">
-      <c r="A332" s="17" t="s">
+      <c r="C389" s="77"/>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B332" s="59" t="s">
+      <c r="B390" s="76" t="s">
         <v>242</v>
       </c>
-      <c r="C332" s="59"/>
-      <c r="E332" s="56"/>
-    </row>
-    <row r="333" spans="1:5">
-      <c r="A333" s="18" t="s">
+      <c r="C390" s="76"/>
+    </row>
+    <row r="391" spans="1:3">
+      <c r="A391" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B333" s="92" t="s">
+      <c r="B391" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C333" s="18" t="s">
+      <c r="C391" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E333" s="56"/>
-    </row>
-    <row r="334" spans="1:5">
-      <c r="A334" s="88" t="s">
+    </row>
+    <row r="392" spans="1:3">
+      <c r="A392" s="58" t="s">
         <v>251</v>
       </c>
-      <c r="B334" t="s">
+      <c r="B392" t="s">
         <v>252</v>
       </c>
-      <c r="C334" s="88" t="s">
+      <c r="C392" s="58" t="s">
         <v>254</v>
       </c>
-      <c r="E334" s="56"/>
-    </row>
-    <row r="335" spans="1:5">
-      <c r="A335" s="88" t="s">
+    </row>
+    <row r="393" spans="1:3">
+      <c r="A393" s="58" t="s">
         <v>253</v>
       </c>
-      <c r="B335" s="93" t="s">
+      <c r="B393" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="C335" s="88" t="s">
+      <c r="C393" s="58" t="s">
         <v>254</v>
       </c>
-      <c r="E335" s="56"/>
-    </row>
-    <row r="336" spans="1:5">
-      <c r="A336" s="88" t="s">
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394" s="58" t="s">
         <v>233</v>
       </c>
-      <c r="B336" s="91"/>
-      <c r="C336" s="88" t="s">
+      <c r="B394" s="61"/>
+      <c r="C394" s="58" t="s">
         <v>255</v>
       </c>
-      <c r="E336" s="57"/>
     </row>
   </sheetData>
-  <mergeCells count="137">
-    <mergeCell ref="A327:C328"/>
-    <mergeCell ref="B330:C330"/>
-    <mergeCell ref="B331:C331"/>
-    <mergeCell ref="B332:C332"/>
-    <mergeCell ref="E329:E336"/>
-    <mergeCell ref="A303:C304"/>
-    <mergeCell ref="B306:C306"/>
-    <mergeCell ref="B307:C307"/>
-    <mergeCell ref="B308:C308"/>
-    <mergeCell ref="A315:C316"/>
-    <mergeCell ref="B318:C318"/>
-    <mergeCell ref="B319:C319"/>
-    <mergeCell ref="B320:C320"/>
-    <mergeCell ref="B295:C295"/>
-    <mergeCell ref="B296:C296"/>
-    <mergeCell ref="C298:C301"/>
-    <mergeCell ref="A291:C292"/>
-    <mergeCell ref="B294:C294"/>
-    <mergeCell ref="A279:C280"/>
-    <mergeCell ref="B282:C282"/>
-    <mergeCell ref="B283:C283"/>
-    <mergeCell ref="B284:C284"/>
-    <mergeCell ref="C275:C277"/>
-    <mergeCell ref="B256:C256"/>
-    <mergeCell ref="B257:C257"/>
-    <mergeCell ref="B258:C258"/>
-    <mergeCell ref="B264:C264"/>
-    <mergeCell ref="B265:C265"/>
-    <mergeCell ref="B266:C266"/>
-    <mergeCell ref="B245:C245"/>
-    <mergeCell ref="B246:C246"/>
-    <mergeCell ref="A253:C254"/>
-    <mergeCell ref="B271:C271"/>
-    <mergeCell ref="B272:C272"/>
-    <mergeCell ref="B273:C273"/>
-    <mergeCell ref="B227:C227"/>
-    <mergeCell ref="B228:C228"/>
-    <mergeCell ref="B235:C235"/>
-    <mergeCell ref="B236:C236"/>
-    <mergeCell ref="B237:C237"/>
-    <mergeCell ref="B244:C244"/>
+  <mergeCells count="167">
+    <mergeCell ref="B212:C212"/>
+    <mergeCell ref="B198:C198"/>
+    <mergeCell ref="B199:C199"/>
+    <mergeCell ref="B203:C203"/>
+    <mergeCell ref="B204:C204"/>
+    <mergeCell ref="B205:C205"/>
     <mergeCell ref="B210:C210"/>
     <mergeCell ref="B211:C211"/>
-    <mergeCell ref="B217:C217"/>
-    <mergeCell ref="B218:C218"/>
-    <mergeCell ref="B219:C219"/>
-    <mergeCell ref="B226:C226"/>
-    <mergeCell ref="B171:C171"/>
-    <mergeCell ref="A197:C198"/>
-    <mergeCell ref="B200:C200"/>
-    <mergeCell ref="B201:C201"/>
-    <mergeCell ref="B202:C202"/>
-    <mergeCell ref="B209:C209"/>
+    <mergeCell ref="B183:C183"/>
+    <mergeCell ref="B184:C184"/>
+    <mergeCell ref="B182:C182"/>
+    <mergeCell ref="B190:C190"/>
+    <mergeCell ref="B191:C191"/>
     <mergeCell ref="B192:C192"/>
-    <mergeCell ref="B193:C193"/>
-    <mergeCell ref="B172:C172"/>
+    <mergeCell ref="B197:C197"/>
+    <mergeCell ref="B168:C168"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="B170:C170"/>
+    <mergeCell ref="B175:C175"/>
+    <mergeCell ref="B176:C176"/>
     <mergeCell ref="B177:C177"/>
-    <mergeCell ref="B178:C178"/>
-    <mergeCell ref="B179:C179"/>
-    <mergeCell ref="C181:C182"/>
-    <mergeCell ref="B185:C185"/>
-    <mergeCell ref="A86:C87"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="A160:C161"/>
-    <mergeCell ref="B186:C186"/>
-    <mergeCell ref="B187:C187"/>
-    <mergeCell ref="B191:C191"/>
+    <mergeCell ref="A159:C160"/>
+    <mergeCell ref="B162:C162"/>
     <mergeCell ref="B163:C163"/>
     <mergeCell ref="B164:C164"/>
-    <mergeCell ref="B165:C165"/>
-    <mergeCell ref="B170:C170"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="C155:C157"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="C116:C118"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
     <mergeCell ref="E79:E86"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -5118,6 +6013,124 @@
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="B65:C65"/>
     <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="C155:C157"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="C116:C118"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="A86:C87"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="A218:C219"/>
+    <mergeCell ref="B244:C244"/>
+    <mergeCell ref="B245:C245"/>
+    <mergeCell ref="B249:C249"/>
+    <mergeCell ref="B221:C221"/>
+    <mergeCell ref="B222:C222"/>
+    <mergeCell ref="B223:C223"/>
+    <mergeCell ref="B228:C228"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B268:C268"/>
+    <mergeCell ref="B269:C269"/>
+    <mergeCell ref="B275:C275"/>
+    <mergeCell ref="B276:C276"/>
+    <mergeCell ref="B277:C277"/>
+    <mergeCell ref="B284:C284"/>
+    <mergeCell ref="B229:C229"/>
+    <mergeCell ref="A255:C256"/>
+    <mergeCell ref="B258:C258"/>
+    <mergeCell ref="B259:C259"/>
+    <mergeCell ref="B260:C260"/>
+    <mergeCell ref="B267:C267"/>
+    <mergeCell ref="B250:C250"/>
+    <mergeCell ref="B251:C251"/>
+    <mergeCell ref="B230:C230"/>
+    <mergeCell ref="B235:C235"/>
+    <mergeCell ref="B236:C236"/>
+    <mergeCell ref="B237:C237"/>
+    <mergeCell ref="C239:C240"/>
+    <mergeCell ref="B243:C243"/>
+    <mergeCell ref="B303:C303"/>
+    <mergeCell ref="B304:C304"/>
+    <mergeCell ref="A311:C312"/>
+    <mergeCell ref="B329:C329"/>
+    <mergeCell ref="B330:C330"/>
+    <mergeCell ref="B331:C331"/>
+    <mergeCell ref="B285:C285"/>
+    <mergeCell ref="B286:C286"/>
+    <mergeCell ref="B293:C293"/>
+    <mergeCell ref="B294:C294"/>
+    <mergeCell ref="B295:C295"/>
+    <mergeCell ref="B302:C302"/>
+    <mergeCell ref="B340:C340"/>
+    <mergeCell ref="B341:C341"/>
+    <mergeCell ref="B342:C342"/>
+    <mergeCell ref="C333:C335"/>
+    <mergeCell ref="B314:C314"/>
+    <mergeCell ref="B315:C315"/>
+    <mergeCell ref="B316:C316"/>
+    <mergeCell ref="B322:C322"/>
+    <mergeCell ref="B323:C323"/>
+    <mergeCell ref="B324:C324"/>
+    <mergeCell ref="E261:E268"/>
+    <mergeCell ref="A385:C386"/>
+    <mergeCell ref="B388:C388"/>
+    <mergeCell ref="B389:C389"/>
+    <mergeCell ref="B390:C390"/>
+    <mergeCell ref="E336:E343"/>
+    <mergeCell ref="E327:E334"/>
+    <mergeCell ref="E313:E320"/>
+    <mergeCell ref="E302:E309"/>
+    <mergeCell ref="E291:E298"/>
+    <mergeCell ref="A361:C362"/>
+    <mergeCell ref="B364:C364"/>
+    <mergeCell ref="B365:C365"/>
+    <mergeCell ref="B366:C366"/>
+    <mergeCell ref="A373:C374"/>
+    <mergeCell ref="B376:C376"/>
+    <mergeCell ref="B377:C377"/>
+    <mergeCell ref="B378:C378"/>
+    <mergeCell ref="B353:C353"/>
+    <mergeCell ref="B354:C354"/>
+    <mergeCell ref="C356:C359"/>
+    <mergeCell ref="A349:C350"/>
+    <mergeCell ref="B352:C352"/>
+    <mergeCell ref="A337:C338"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5148,23 +6161,23 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="95" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="97" t="s">
         <v>192</v>
       </c>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -5193,7 +6206,7 @@
       <c r="C5" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="79" t="s">
+      <c r="D5" s="93" t="s">
         <v>202</v>
       </c>
     </row>
@@ -5207,7 +6220,7 @@
       <c r="C6" t="s">
         <v>200</v>
       </c>
-      <c r="D6" s="85"/>
+      <c r="D6" s="99"/>
     </row>
     <row r="7" spans="1:5" ht="15">
       <c r="A7" s="36" t="s">
@@ -5219,7 +6232,7 @@
       <c r="C7" t="s">
         <v>201</v>
       </c>
-      <c r="D7" s="85"/>
+      <c r="D7" s="99"/>
     </row>
     <row r="8" spans="1:5" ht="15">
       <c r="A8" s="36" t="s">
@@ -5241,23 +6254,23 @@
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="81" t="s">
+      <c r="B17" s="95" t="s">
         <v>204</v>
       </c>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="96"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="100" t="s">
         <v>205</v>
       </c>
-      <c r="C18" s="84"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
@@ -5286,7 +6299,7 @@
       <c r="C20" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="D20" s="79" t="s">
+      <c r="D20" s="93" t="s">
         <v>202</v>
       </c>
     </row>
@@ -5300,7 +6313,7 @@
       <c r="C21" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="D21" s="80"/>
+      <c r="D21" s="94"/>
     </row>
     <row r="22" spans="1:5" ht="43.2">
       <c r="A22" s="37" t="s">
@@ -5312,7 +6325,7 @@
       <c r="C22" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="D22" s="80"/>
+      <c r="D22" s="94"/>
     </row>
     <row r="23" spans="1:5" ht="43.2">
       <c r="A23" s="37" t="s">
@@ -5324,7 +6337,7 @@
       <c r="C23" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="D23" s="80"/>
+      <c r="D23" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/SauceDemoTC&BR.xlsx
+++ b/SauceDemoTC&BR.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="347">
   <si>
     <t>ID</t>
   </si>
@@ -1038,6 +1038,220 @@
   </si>
   <si>
     <t>User is redirected back to the inventory page. All products are displayed in their default state, with buttons showing Add to cart and no cart badge visible</t>
+  </si>
+  <si>
+    <t>Test Case - Product Detail Page</t>
+  </si>
+  <si>
+    <t>TC- ITEM-1</t>
+  </si>
+  <si>
+    <t>User is logged in with valid credentials, and he is on inventory page</t>
+  </si>
+  <si>
+    <t>Click “Add to cart” button on Inventory Page for Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cart badge shows </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Button changes to </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Remove</t>
+    </r>
+  </si>
+  <si>
+    <t>Navigate to Product Detail Page for Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Button state is synchronized and shows </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Remove</t>
+    </r>
+  </si>
+  <si>
+    <t>Click “Remove” button on Product Detail Page</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Product is removed from cart. Cart badge disappears. Button resets to </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Add to cart</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> both on Product Detail Page and Inventory Page</t>
+    </r>
+  </si>
+  <si>
+    <t>Click “Add to cart” button again on Product Detail Page</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Product is added back to the cart. Cart badge shows </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Button changes to </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Remove</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> both on Product Detail Page and Inventory Page</t>
+    </r>
+  </si>
+  <si>
+    <t>Click cart icon in header</t>
+  </si>
+  <si>
+    <t>User is redirected to the cart page. The cart page displays Sauce Labs Backpack with correct name, price, and quantity</t>
+  </si>
+  <si>
+    <t>Navigate Back to Product Detail Page</t>
+  </si>
+  <si>
+    <t>Click “Back to products” button</t>
+  </si>
+  <si>
+    <t>User is redirected back to Inventory Page</t>
+  </si>
+  <si>
+    <t>User is redirected to the Product Detail Page</t>
+  </si>
+  <si>
+    <t>Verify product detail page for Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>Compare product details between Inventory Page and Product Detail Page</t>
+  </si>
+  <si>
+    <t>TC-ITEM-2</t>
+  </si>
+  <si>
+    <t>Locate Sauce Labs Backpack on Inventory Page</t>
+  </si>
+  <si>
+    <t>Click product name or image to open Product Detail Page</t>
+  </si>
+  <si>
+    <t>Verify product name on Product Detail Page</t>
+  </si>
+  <si>
+    <t>Verify product price on Product Detail Page</t>
+  </si>
+  <si>
+    <t>Verify product description on Product Detail Page</t>
+  </si>
+  <si>
+    <t>Verify product image on Product Detail Page</t>
+  </si>
+  <si>
+    <t>Product card shows name Sauce Labs Backpack, price $29.99, adequate photo, and short description</t>
+  </si>
+  <si>
+    <t>User is redirected to product detail page for Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>Product name matches inventory page (“Sauce Labs Backpack”)</t>
+  </si>
+  <si>
+    <t>Price matches inventory page ($29.99)</t>
+  </si>
+  <si>
+    <t>Full description is displayed, consistent with the short summary shown on inventory page</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Larger product image is displayed, consistent with image on inventory page</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1687,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1602,93 +1816,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1700,16 +1830,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1717,39 +1838,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1764,15 +1852,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1792,6 +1871,144 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1910,13 +2127,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>314</xdr:row>
+      <xdr:row>299</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>314</xdr:row>
+      <xdr:row>299</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1957,13 +2174,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>303</xdr:row>
+      <xdr:row>288</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>303</xdr:row>
+      <xdr:row>288</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2004,13 +2221,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>293</xdr:row>
+      <xdr:row>278</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>293</xdr:row>
+      <xdr:row>278</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2051,13 +2268,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>263</xdr:row>
+      <xdr:row>248</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>263</xdr:row>
+      <xdr:row>248</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2621,7 +2838,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2629,7 +2846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E393"/>
+  <dimension ref="A1:E418"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="39.77734375" style="2" bestFit="1" customWidth="1"/>
@@ -2640,30 +2857,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="78" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="E1" s="67" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="E1" s="76" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="E2" s="68"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="59"/>
-      <c r="E5" s="50" t="s">
+      <c r="C5" s="70"/>
+      <c r="E5" s="73" t="s">
         <v>210</v>
       </c>
     </row>
@@ -2671,21 +2888,21 @@
       <c r="A6" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="60"/>
-      <c r="E6" s="51"/>
+      <c r="C6" s="71"/>
+      <c r="E6" s="74"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="59"/>
-      <c r="E7" s="51"/>
+      <c r="C7" s="70"/>
+      <c r="E7" s="74"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="11" t="s">
@@ -2697,7 +2914,7 @@
       <c r="C8" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="51"/>
+      <c r="E8" s="74"/>
     </row>
     <row r="9" spans="1:5" ht="27">
       <c r="A9" s="12" t="s">
@@ -2710,7 +2927,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="34"/>
-      <c r="E9" s="51"/>
+      <c r="E9" s="74"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="12" t="s">
@@ -2722,7 +2939,7 @@
       <c r="C10" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="51"/>
+      <c r="E10" s="74"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="12" t="s">
@@ -2734,7 +2951,7 @@
       <c r="C11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="51"/>
+      <c r="E11" s="74"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="12" t="s">
@@ -2746,7 +2963,7 @@
       <c r="C12" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="52"/>
+      <c r="E12" s="75"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3"/>
@@ -2757,28 +2974,28 @@
       <c r="A15" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="59" t="s">
+      <c r="B15" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="59"/>
+      <c r="C15" s="70"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="60" t="s">
+      <c r="B16" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="60"/>
+      <c r="C16" s="71"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="59" t="s">
+      <c r="B17" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="59"/>
+      <c r="C17" s="70"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="11" t="s">
@@ -2828,28 +3045,28 @@
       <c r="A23" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="59" t="s">
+      <c r="B23" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="59"/>
+      <c r="C23" s="70"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="60" t="s">
+      <c r="B24" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="60"/>
+      <c r="C24" s="71"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="59" t="s">
+      <c r="B25" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="59"/>
+      <c r="C25" s="70"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="11" t="s">
@@ -2899,28 +3116,28 @@
       <c r="A31" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="59"/>
+      <c r="C31" s="70"/>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="60"/>
+      <c r="C32" s="71"/>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="59" t="s">
+      <c r="B33" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="59"/>
+      <c r="C33" s="70"/>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="11" t="s">
@@ -2970,28 +3187,28 @@
       <c r="A40" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="59" t="s">
+      <c r="B40" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="70"/>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B41" s="60" t="s">
+      <c r="B41" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="C41" s="60"/>
+      <c r="C41" s="71"/>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="59" t="s">
+      <c r="B42" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="59"/>
+      <c r="C42" s="70"/>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="11" t="s">
@@ -3041,28 +3258,28 @@
       <c r="A48" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="59" t="s">
+      <c r="B48" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="C48" s="59"/>
+      <c r="C48" s="70"/>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="60" t="s">
+      <c r="B49" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="60"/>
+      <c r="C49" s="71"/>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="59" t="s">
+      <c r="B50" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="59"/>
+      <c r="C50" s="70"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="11" t="s">
@@ -3112,28 +3329,28 @@
       <c r="A56" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B56" s="59" t="s">
+      <c r="B56" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="59"/>
+      <c r="C56" s="70"/>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B57" s="60" t="s">
+      <c r="B57" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="C57" s="60"/>
+      <c r="C57" s="71"/>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B58" s="59" t="s">
+      <c r="B58" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="C58" s="59"/>
+      <c r="C58" s="70"/>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="11" t="s">
@@ -3183,28 +3400,28 @@
       <c r="A64" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B64" s="59" t="s">
+      <c r="B64" s="70" t="s">
         <v>35</v>
       </c>
-      <c r="C64" s="59"/>
+      <c r="C64" s="70"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B65" s="60" t="s">
+      <c r="B65" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="C65" s="60"/>
+      <c r="C65" s="71"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B66" s="59" t="s">
+      <c r="B66" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="C66" s="59"/>
+      <c r="C66" s="70"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="11" t="s">
@@ -3243,28 +3460,28 @@
       <c r="A71" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B71" s="59" t="s">
+      <c r="B71" s="70" t="s">
         <v>38</v>
       </c>
-      <c r="C71" s="59"/>
+      <c r="C71" s="70"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B72" s="60" t="s">
+      <c r="B72" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="C72" s="60"/>
+      <c r="C72" s="71"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B73" s="59" t="s">
+      <c r="B73" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="C73" s="59"/>
+      <c r="C73" s="70"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="11" t="s">
@@ -3319,11 +3536,11 @@
       <c r="A79" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B79" s="59" t="s">
+      <c r="B79" s="70" t="s">
         <v>212</v>
       </c>
-      <c r="C79" s="59"/>
-      <c r="E79" s="50" t="s">
+      <c r="C79" s="70"/>
+      <c r="E79" s="73" t="s">
         <v>210</v>
       </c>
     </row>
@@ -3331,21 +3548,21 @@
       <c r="A80" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B80" s="60" t="s">
+      <c r="B80" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="C80" s="60"/>
-      <c r="E80" s="51"/>
+      <c r="C80" s="71"/>
+      <c r="E80" s="74"/>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B81" s="59" t="s">
+      <c r="B81" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="C81" s="59"/>
-      <c r="E81" s="51"/>
+      <c r="C81" s="70"/>
+      <c r="E81" s="74"/>
     </row>
     <row r="82" spans="1:5" ht="14.4" customHeight="1">
       <c r="A82" s="11" t="s">
@@ -3357,7 +3574,7 @@
       <c r="C82" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E82" s="51"/>
+      <c r="E82" s="74"/>
     </row>
     <row r="83" spans="1:5" ht="29.4">
       <c r="A83" s="36" t="s">
@@ -3367,56 +3584,56 @@
       <c r="C83" s="37" t="s">
         <v>216</v>
       </c>
-      <c r="E83" s="51"/>
+      <c r="E83" s="74"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="7"/>
       <c r="B84" s="35"/>
       <c r="C84" s="7"/>
-      <c r="E84" s="51"/>
+      <c r="E84" s="74"/>
     </row>
     <row r="85" spans="1:5" ht="15" thickBot="1">
-      <c r="E85" s="51"/>
+      <c r="E85" s="74"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="53" t="s">
+      <c r="A86" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="B86" s="54"/>
-      <c r="C86" s="55"/>
-      <c r="E86" s="52"/>
+      <c r="B86" s="79"/>
+      <c r="C86" s="80"/>
+      <c r="E86" s="75"/>
     </row>
     <row r="87" spans="1:5" ht="15" thickBot="1">
-      <c r="A87" s="56"/>
-      <c r="B87" s="57"/>
-      <c r="C87" s="58"/>
+      <c r="A87" s="81"/>
+      <c r="B87" s="82"/>
+      <c r="C87" s="83"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B90" s="59" t="s">
+      <c r="B90" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="C90" s="59"/>
+      <c r="C90" s="70"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B91" s="60" t="s">
+      <c r="B91" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="C91" s="60"/>
+      <c r="C91" s="71"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B92" s="59" t="s">
+      <c r="B92" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C92" s="59"/>
+      <c r="C92" s="70"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="11" t="s">
@@ -3460,28 +3677,28 @@
       <c r="A98" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B98" s="59" t="s">
+      <c r="B98" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="C98" s="59"/>
+      <c r="C98" s="70"/>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B99" s="60" t="s">
+      <c r="B99" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="C99" s="60"/>
+      <c r="C99" s="71"/>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B100" s="59" t="s">
+      <c r="B100" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C100" s="59"/>
+      <c r="C100" s="70"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="11" t="s">
@@ -3514,28 +3731,28 @@
       <c r="A105" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B105" s="59" t="s">
+      <c r="B105" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="C105" s="59"/>
+      <c r="C105" s="70"/>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B106" s="60" t="s">
+      <c r="B106" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="C106" s="60"/>
+      <c r="C106" s="71"/>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B107" s="59" t="s">
+      <c r="B107" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C107" s="59"/>
+      <c r="C107" s="70"/>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="11" t="s">
@@ -3566,28 +3783,28 @@
       <c r="A112" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B112" s="59" t="s">
+      <c r="B112" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="C112" s="59"/>
+      <c r="C112" s="70"/>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B113" s="60" t="s">
+      <c r="B113" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="C113" s="60"/>
+      <c r="C113" s="71"/>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B114" s="59" t="s">
+      <c r="B114" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C114" s="59"/>
+      <c r="C114" s="70"/>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="11" t="s">
@@ -3637,28 +3854,28 @@
       <c r="A121" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B121" s="59" t="s">
+      <c r="B121" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="C121" s="59"/>
+      <c r="C121" s="70"/>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B122" s="60" t="s">
+      <c r="B122" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="C122" s="60"/>
+      <c r="C122" s="71"/>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B123" s="59" t="s">
+      <c r="B123" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="C123" s="59"/>
+      <c r="C123" s="70"/>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="11" t="s">
@@ -3691,28 +3908,28 @@
       <c r="A128" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B128" s="59" t="s">
+      <c r="B128" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="C128" s="59"/>
+      <c r="C128" s="70"/>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B129" s="60" t="s">
+      <c r="B129" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="C129" s="60"/>
+      <c r="C129" s="71"/>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B130" s="59" t="s">
+      <c r="B130" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="C130" s="59"/>
+      <c r="C130" s="70"/>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="11" t="s">
@@ -3756,28 +3973,28 @@
       <c r="A136" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B136" s="59" t="s">
+      <c r="B136" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="59"/>
+      <c r="C136" s="70"/>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B137" s="60" t="s">
+      <c r="B137" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="C137" s="60"/>
+      <c r="C137" s="71"/>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B138" s="59" t="s">
+      <c r="B138" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="C138" s="59"/>
+      <c r="C138" s="70"/>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="11" t="s">
@@ -3821,28 +4038,28 @@
       <c r="A144" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B144" s="59" t="s">
+      <c r="B144" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="C144" s="59"/>
+      <c r="C144" s="70"/>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B145" s="60" t="s">
+      <c r="B145" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="C145" s="60"/>
+      <c r="C145" s="71"/>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B146" s="59" t="s">
+      <c r="B146" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="C146" s="59"/>
+      <c r="C146" s="70"/>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="11" t="s">
@@ -3886,30 +4103,30 @@
       <c r="A151" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B151" s="59" t="s">
+      <c r="B151" s="70" t="s">
         <v>86</v>
       </c>
-      <c r="C151" s="59"/>
+      <c r="C151" s="70"/>
       <c r="E151" s="3"/>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B152" s="60" t="s">
+      <c r="B152" s="71" t="s">
         <v>87</v>
       </c>
-      <c r="C152" s="60"/>
+      <c r="C152" s="71"/>
       <c r="E152" s="3"/>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B153" s="59" t="s">
+      <c r="B153" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="C153" s="59"/>
+      <c r="C153" s="70"/>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="11" t="s">
@@ -3950,16 +4167,16 @@
       <c r="C157" s="9"/>
     </row>
     <row r="158" spans="1:5">
-      <c r="A158" s="62" t="s">
+      <c r="A158" s="72" t="s">
         <v>248</v>
       </c>
-      <c r="B158" s="62"/>
-      <c r="C158" s="62"/>
+      <c r="B158" s="72"/>
+      <c r="C158" s="72"/>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="62"/>
-      <c r="B159" s="62"/>
-      <c r="C159" s="62"/>
+      <c r="A159" s="72"/>
+      <c r="B159" s="72"/>
+      <c r="C159" s="72"/>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="7"/>
@@ -3970,28 +4187,28 @@
       <c r="A161" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B161" s="59" t="s">
+      <c r="B161" s="70" t="s">
         <v>249</v>
       </c>
-      <c r="C161" s="59"/>
+      <c r="C161" s="70"/>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B162" s="60" t="s">
+      <c r="B162" s="71" t="s">
         <v>250</v>
       </c>
-      <c r="C162" s="60"/>
+      <c r="C162" s="71"/>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B163" s="59" t="s">
+      <c r="B163" s="70" t="s">
         <v>251</v>
       </c>
-      <c r="C163" s="59"/>
+      <c r="C163" s="70"/>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" s="11" t="s">
@@ -4005,7 +4222,7 @@
       </c>
     </row>
     <row r="165" spans="1:3" ht="28.8">
-      <c r="A165" s="79" t="s">
+      <c r="A165" s="51" t="s">
         <v>252</v>
       </c>
       <c r="B165" s="13"/>
@@ -4022,28 +4239,28 @@
       <c r="A167" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B167" s="59" t="s">
+      <c r="B167" s="70" t="s">
         <v>255</v>
       </c>
-      <c r="C167" s="59"/>
+      <c r="C167" s="70"/>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B168" s="60" t="s">
+      <c r="B168" s="71" t="s">
         <v>254</v>
       </c>
-      <c r="C168" s="60"/>
+      <c r="C168" s="71"/>
     </row>
     <row r="169" spans="1:3" ht="14.4" customHeight="1">
       <c r="A169" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B169" s="59" t="s">
+      <c r="B169" s="70" t="s">
         <v>251</v>
       </c>
-      <c r="C169" s="59"/>
+      <c r="C169" s="70"/>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" s="11" t="s">
@@ -4083,28 +4300,28 @@
       <c r="A174" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B174" s="59" t="s">
+      <c r="B174" s="70" t="s">
         <v>259</v>
       </c>
-      <c r="C174" s="59"/>
+      <c r="C174" s="70"/>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B175" s="60" t="s">
+      <c r="B175" s="71" t="s">
         <v>263</v>
       </c>
-      <c r="C175" s="60"/>
+      <c r="C175" s="71"/>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B176" s="59" t="s">
+      <c r="B176" s="70" t="s">
         <v>251</v>
       </c>
-      <c r="C176" s="59"/>
+      <c r="C176" s="70"/>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="11" t="s">
@@ -4144,28 +4361,28 @@
       <c r="A181" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B181" s="59" t="s">
+      <c r="B181" s="70" t="s">
         <v>262</v>
       </c>
-      <c r="C181" s="59"/>
+      <c r="C181" s="70"/>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B182" s="60" t="s">
+      <c r="B182" s="71" t="s">
         <v>264</v>
       </c>
-      <c r="C182" s="60"/>
+      <c r="C182" s="71"/>
     </row>
     <row r="183" spans="1:3" ht="14.4" customHeight="1">
       <c r="A183" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B183" s="59" t="s">
+      <c r="B183" s="70" t="s">
         <v>251</v>
       </c>
-      <c r="C183" s="59"/>
+      <c r="C183" s="70"/>
     </row>
     <row r="184" spans="1:3" ht="14.4" customHeight="1">
       <c r="A184" s="11" t="s">
@@ -4188,11 +4405,11 @@
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="80" t="s">
+      <c r="A186" s="52" t="s">
         <v>265</v>
       </c>
-      <c r="B186" s="80"/>
-      <c r="C186" s="80" t="s">
+      <c r="B186" s="52"/>
+      <c r="C186" s="52" t="s">
         <v>266</v>
       </c>
     </row>
@@ -4210,28 +4427,28 @@
       <c r="A189" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B189" s="59" t="s">
+      <c r="B189" s="70" t="s">
         <v>267</v>
       </c>
-      <c r="C189" s="59"/>
+      <c r="C189" s="70"/>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B190" s="60" t="s">
+      <c r="B190" s="71" t="s">
         <v>268</v>
       </c>
-      <c r="C190" s="60"/>
+      <c r="C190" s="71"/>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B191" s="59" t="s">
+      <c r="B191" s="70" t="s">
         <v>269</v>
       </c>
-      <c r="C191" s="59"/>
+      <c r="C191" s="70"/>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="11" t="s">
@@ -4271,28 +4488,28 @@
       <c r="A196" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B196" s="59" t="s">
+      <c r="B196" s="70" t="s">
         <v>272</v>
       </c>
-      <c r="C196" s="59"/>
+      <c r="C196" s="70"/>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B197" s="60" t="s">
+      <c r="B197" s="71" t="s">
         <v>271</v>
       </c>
-      <c r="C197" s="60"/>
+      <c r="C197" s="71"/>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B198" s="59" t="s">
+      <c r="B198" s="70" t="s">
         <v>273</v>
       </c>
-      <c r="C198" s="59"/>
+      <c r="C198" s="70"/>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="11" t="s">
@@ -4323,28 +4540,28 @@
       <c r="A202" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B202" s="59" t="s">
+      <c r="B202" s="70" t="s">
         <v>277</v>
       </c>
-      <c r="C202" s="59"/>
+      <c r="C202" s="70"/>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B203" s="60" t="s">
+      <c r="B203" s="71" t="s">
         <v>276</v>
       </c>
-      <c r="C203" s="60"/>
+      <c r="C203" s="71"/>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B204" s="59" t="s">
+      <c r="B204" s="70" t="s">
         <v>269</v>
       </c>
-      <c r="C204" s="59"/>
+      <c r="C204" s="70"/>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" s="11" t="s">
@@ -4384,28 +4601,28 @@
       <c r="A209" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B209" s="59" t="s">
+      <c r="B209" s="70" t="s">
         <v>278</v>
       </c>
-      <c r="C209" s="59"/>
+      <c r="C209" s="70"/>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B210" s="60" t="s">
+      <c r="B210" s="71" t="s">
         <v>282</v>
       </c>
-      <c r="C210" s="60"/>
+      <c r="C210" s="71"/>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B211" s="59" t="s">
+      <c r="B211" s="70" t="s">
         <v>283</v>
       </c>
-      <c r="C211" s="59"/>
+      <c r="C211" s="70"/>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" s="11" t="s">
@@ -4437,1036 +4654,1089 @@
       </c>
     </row>
     <row r="215" spans="1:3">
-      <c r="A215" s="38"/>
+      <c r="A215" s="50"/>
       <c r="B215" s="13"/>
-      <c r="C215" s="38"/>
+      <c r="C215" s="50"/>
     </row>
     <row r="216" spans="1:3">
-      <c r="A216" s="7"/>
-      <c r="B216" s="8"/>
-      <c r="C216" s="9"/>
+      <c r="A216" s="84" t="s">
+        <v>315</v>
+      </c>
+      <c r="B216" s="85"/>
+      <c r="C216" s="86"/>
+    </row>
+    <row r="217" spans="1:3">
+      <c r="A217" s="87"/>
+      <c r="B217" s="88"/>
+      <c r="C217" s="89"/>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="71" t="s">
-        <v>161</v>
-      </c>
-      <c r="B218" s="72"/>
-      <c r="C218" s="73"/>
+      <c r="A218" s="50"/>
+      <c r="B218" s="13"/>
+      <c r="C218" s="50"/>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="74"/>
-      <c r="B219" s="75"/>
-      <c r="C219" s="76"/>
+      <c r="A219" s="7"/>
+      <c r="B219" s="8"/>
+      <c r="C219" s="7"/>
+    </row>
+    <row r="220" spans="1:3">
+      <c r="A220" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B220" s="70" t="s">
+        <v>316</v>
+      </c>
+      <c r="C220" s="70"/>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B221" s="69" t="s">
-        <v>89</v>
-      </c>
-      <c r="C221" s="70"/>
+        <v>1</v>
+      </c>
+      <c r="B221" s="71" t="s">
+        <v>332</v>
+      </c>
+      <c r="C221" s="71"/>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B222" s="77" t="s">
-        <v>90</v>
-      </c>
-      <c r="C222" s="78"/>
+        <v>23</v>
+      </c>
+      <c r="B222" s="70" t="s">
+        <v>317</v>
+      </c>
+      <c r="C222" s="70"/>
     </row>
     <row r="223" spans="1:3">
-      <c r="A223" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B223" s="59" t="s">
-        <v>107</v>
-      </c>
-      <c r="C223" s="59"/>
-    </row>
-    <row r="224" spans="1:3">
-      <c r="A224" s="11" t="s">
+      <c r="A223" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B224" s="11" t="s">
+      <c r="B223" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C224" s="11" t="s">
+      <c r="C223" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:3">
-      <c r="A225" s="12" t="s">
-        <v>91</v>
+    <row r="224" spans="1:3" ht="29.4">
+      <c r="A224" s="51" t="s">
+        <v>318</v>
+      </c>
+      <c r="B224" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C224" s="41" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="28.8">
+      <c r="A225" s="51" t="s">
+        <v>320</v>
       </c>
       <c r="B225" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C225" s="18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" ht="15" thickBot="1">
-      <c r="A226" s="5"/>
-      <c r="B226" s="22"/>
-      <c r="C226" s="5"/>
-    </row>
-    <row r="228" spans="1:3">
-      <c r="A228" s="10" t="s">
+      <c r="C225" s="41" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="28.8">
+      <c r="A226" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="B226" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C226" s="51" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="29.4">
+      <c r="A227" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="B227" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C227" s="51" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="28.8">
+      <c r="A228" s="51" t="s">
+        <v>326</v>
+      </c>
+      <c r="B228" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C228" s="51" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229" s="51" t="s">
+        <v>328</v>
+      </c>
+      <c r="B229" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C229" s="51" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230" s="51" t="s">
+        <v>329</v>
+      </c>
+      <c r="B230" s="13"/>
+      <c r="C230" s="41" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231" s="7"/>
+      <c r="B231" s="8"/>
+      <c r="C231" s="7"/>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B228" s="59" t="s">
-        <v>93</v>
-      </c>
-      <c r="C228" s="59"/>
-    </row>
-    <row r="229" spans="1:3">
-      <c r="A229" s="10" t="s">
+      <c r="B232" s="70" t="s">
+        <v>334</v>
+      </c>
+      <c r="C232" s="70"/>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B229" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="C229" s="60"/>
-    </row>
-    <row r="230" spans="1:3">
-      <c r="A230" s="10" t="s">
+      <c r="B233" s="71" t="s">
+        <v>333</v>
+      </c>
+      <c r="C233" s="71"/>
+    </row>
+    <row r="234" spans="1:3" ht="14.4" customHeight="1">
+      <c r="A234" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B230" s="59" t="s">
-        <v>107</v>
-      </c>
-      <c r="C230" s="59"/>
-    </row>
-    <row r="231" spans="1:3">
-      <c r="A231" s="11" t="s">
+      <c r="B234" s="70" t="s">
+        <v>317</v>
+      </c>
+      <c r="C234" s="70"/>
+    </row>
+    <row r="235" spans="1:3" ht="14.4" customHeight="1">
+      <c r="A235" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B231" s="11" t="s">
+      <c r="B235" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C231" s="11" t="s">
+      <c r="C235" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:3">
-      <c r="A232" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="B232" s="13" t="s">
+    <row r="236" spans="1:3" ht="28.8">
+      <c r="A236" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="B236" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C232" s="39" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" ht="15" thickBot="1">
-      <c r="A233" s="5"/>
-      <c r="B233" s="22"/>
-      <c r="C233" s="5"/>
-    </row>
-    <row r="235" spans="1:3">
-      <c r="A235" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B235" s="59" t="s">
-        <v>96</v>
-      </c>
-      <c r="C235" s="59"/>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B236" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C236" s="60"/>
-    </row>
-    <row r="237" spans="1:3">
-      <c r="A237" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B237" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="C237" s="59"/>
+      <c r="C236" s="51" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="27">
+      <c r="A237" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="B237" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C237" s="50" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B238" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C238" s="11" t="s">
-        <v>4</v>
+      <c r="A238" s="50" t="s">
+        <v>337</v>
+      </c>
+      <c r="B238" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C238" s="51" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="239" spans="1:3">
-      <c r="A239" s="12" t="s">
-        <v>91</v>
+      <c r="A239" s="50" t="s">
+        <v>338</v>
       </c>
       <c r="B239" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C239" s="38" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
-      <c r="A240" s="12" t="s">
-        <v>99</v>
+      <c r="C239" s="50" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="27">
+      <c r="A240" s="50" t="s">
+        <v>339</v>
       </c>
       <c r="B240" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C240" s="38" t="s">
+      <c r="C240" s="50" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="B241" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C241" s="24" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="84" t="s">
+        <v>161</v>
+      </c>
+      <c r="B243" s="85"/>
+      <c r="C243" s="86"/>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="87"/>
+      <c r="B244" s="88"/>
+      <c r="C244" s="89"/>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B246" s="90" t="s">
+        <v>89</v>
+      </c>
+      <c r="C246" s="91"/>
+      <c r="E246" s="73" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B247" s="92" t="s">
+        <v>90</v>
+      </c>
+      <c r="C247" s="93"/>
+      <c r="E247" s="74"/>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B248" s="70" t="s">
+        <v>107</v>
+      </c>
+      <c r="C248" s="70"/>
+      <c r="E248" s="74"/>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B249" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C249" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E249" s="74"/>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B250" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C250" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E250" s="74"/>
+    </row>
+    <row r="251" spans="1:5" ht="15" thickBot="1">
+      <c r="A251" s="5"/>
+      <c r="B251" s="22"/>
+      <c r="C251" s="5"/>
+      <c r="E251" s="74"/>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="E252" s="74"/>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B253" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="C253" s="70"/>
+      <c r="E253" s="75"/>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B254" s="71" t="s">
+        <v>94</v>
+      </c>
+      <c r="C254" s="71"/>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B255" s="70" t="s">
+        <v>107</v>
+      </c>
+      <c r="C255" s="70"/>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B256" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C256" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3">
+      <c r="A257" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="B257" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C257" s="39" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="15" thickBot="1">
+      <c r="A258" s="5"/>
+      <c r="B258" s="22"/>
+      <c r="C258" s="5"/>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B260" s="70" t="s">
+        <v>96</v>
+      </c>
+      <c r="C260" s="70"/>
+    </row>
+    <row r="261" spans="1:3">
+      <c r="A261" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B261" s="71" t="s">
+        <v>97</v>
+      </c>
+      <c r="C261" s="71"/>
+    </row>
+    <row r="262" spans="1:3">
+      <c r="A262" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B262" s="70" t="s">
+        <v>98</v>
+      </c>
+      <c r="C262" s="70"/>
+    </row>
+    <row r="263" spans="1:3">
+      <c r="A263" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B263" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C263" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B264" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C264" s="38" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="A265" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B265" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C265" s="38" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="243" spans="1:3">
-      <c r="A243" s="10" t="s">
+    <row r="268" spans="1:3">
+      <c r="A268" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B243" s="59" t="s">
+      <c r="B268" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="C243" s="59"/>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244" s="10" t="s">
+      <c r="C268" s="70"/>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B244" s="60" t="s">
+      <c r="B269" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="C244" s="60"/>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245" s="10" t="s">
+      <c r="C269" s="71"/>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B245" s="59" t="s">
+      <c r="B270" s="70" t="s">
         <v>103</v>
       </c>
-      <c r="C245" s="59"/>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246" s="11" t="s">
+      <c r="C270" s="70"/>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B246" s="11" t="s">
+      <c r="B271" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C246" s="11" t="s">
+      <c r="C271" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="1:3">
-      <c r="A247" s="12" t="s">
+    <row r="272" spans="1:3">
+      <c r="A272" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B247" s="13" t="s">
+      <c r="B272" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C247" s="12" t="s">
+      <c r="C272" s="12" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="248" spans="1:3">
-      <c r="A248" s="4"/>
-      <c r="B248" s="23"/>
-      <c r="C248" s="6"/>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249" s="10" t="s">
+    <row r="273" spans="1:5">
+      <c r="A273" s="4"/>
+      <c r="B273" s="23"/>
+      <c r="C273" s="6"/>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B249" s="59" t="s">
+      <c r="B274" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="C249" s="59"/>
-    </row>
-    <row r="250" spans="1:3">
-      <c r="A250" s="10" t="s">
+      <c r="C274" s="70"/>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B250" s="60" t="s">
+      <c r="B275" s="71" t="s">
         <v>109</v>
       </c>
-      <c r="C250" s="60"/>
-    </row>
-    <row r="251" spans="1:3">
-      <c r="A251" s="10" t="s">
+      <c r="C275" s="71"/>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B251" s="59" t="s">
+      <c r="B276" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="C251" s="59"/>
-    </row>
-    <row r="252" spans="1:3">
-      <c r="A252" s="11" t="s">
+      <c r="C276" s="70"/>
+      <c r="E276" s="73" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B252" s="11" t="s">
+      <c r="B277" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C252" s="11" t="s">
+      <c r="C277" s="11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="253" spans="1:3">
-      <c r="A253" s="12" t="s">
+      <c r="E277" s="74"/>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B253" s="13" t="s">
+      <c r="B278" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C253" s="12" t="s">
+      <c r="C278" s="12" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" ht="15" thickBot="1"/>
-    <row r="255" spans="1:3">
-      <c r="A255" s="53" t="s">
+      <c r="E278" s="74"/>
+    </row>
+    <row r="279" spans="1:5" ht="15" thickBot="1">
+      <c r="E279" s="74"/>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="78" t="s">
         <v>162</v>
       </c>
-      <c r="B255" s="54"/>
-      <c r="C255" s="55"/>
-    </row>
-    <row r="256" spans="1:3" ht="15" thickBot="1">
-      <c r="A256" s="56"/>
-      <c r="B256" s="57"/>
-      <c r="C256" s="58"/>
-    </row>
-    <row r="258" spans="1:5">
-      <c r="A258" s="10" t="s">
+      <c r="B280" s="79"/>
+      <c r="C280" s="80"/>
+      <c r="E280" s="74"/>
+    </row>
+    <row r="281" spans="1:5" ht="15" thickBot="1">
+      <c r="A281" s="81"/>
+      <c r="B281" s="82"/>
+      <c r="C281" s="83"/>
+      <c r="E281" s="74"/>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="E282" s="74"/>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B258" s="65" t="s">
+      <c r="B283" s="94" t="s">
         <v>112</v>
       </c>
-      <c r="C258" s="65"/>
-    </row>
-    <row r="259" spans="1:5">
-      <c r="A259" s="10" t="s">
+      <c r="C283" s="94"/>
+      <c r="E283" s="75"/>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B259" s="60" t="s">
+      <c r="B284" s="71" t="s">
         <v>117</v>
       </c>
-      <c r="C259" s="60"/>
-    </row>
-    <row r="260" spans="1:5">
-      <c r="A260" s="10" t="s">
+      <c r="C284" s="71"/>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B260" s="59" t="s">
+      <c r="B285" s="70" t="s">
         <v>127</v>
       </c>
-      <c r="C260" s="59"/>
-    </row>
-    <row r="261" spans="1:5">
-      <c r="A261" s="11" t="s">
+      <c r="C285" s="70"/>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B261" s="11" t="s">
+      <c r="B286" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C261" s="11" t="s">
+      <c r="C286" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E261" s="50" t="s">
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B287" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C287" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E287" s="73" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
-      <c r="A262" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B262" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C262" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E262" s="51"/>
-    </row>
-    <row r="263" spans="1:5">
-      <c r="A263" s="12" t="s">
+    <row r="288" spans="1:5">
+      <c r="A288" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B263" s="13" t="s">
+      <c r="B288" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C263" s="19" t="s">
+      <c r="C288" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="E263" s="51"/>
-    </row>
-    <row r="264" spans="1:5">
-      <c r="A264" s="47" t="s">
+      <c r="E288" s="74"/>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="B264" s="48">
+      <c r="B289" s="48">
         <v>18000</v>
       </c>
-      <c r="C264" s="49" t="s">
+      <c r="C289" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="E264" s="51"/>
-    </row>
-    <row r="265" spans="1:5">
-      <c r="A265" s="47" t="s">
+      <c r="E289" s="74"/>
+    </row>
+    <row r="290" spans="1:5" ht="14.4" customHeight="1">
+      <c r="A290" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="B265" s="47"/>
-      <c r="C265" s="49" t="s">
+      <c r="B290" s="47"/>
+      <c r="C290" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="E265" s="51"/>
-    </row>
-    <row r="266" spans="1:5">
-      <c r="E266" s="51"/>
-    </row>
-    <row r="267" spans="1:5">
-      <c r="A267" s="10" t="s">
+      <c r="E290" s="74"/>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="E291" s="74"/>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B267" s="65" t="s">
+      <c r="B292" s="94" t="s">
         <v>113</v>
       </c>
-      <c r="C267" s="65"/>
-      <c r="E267" s="51"/>
-    </row>
-    <row r="268" spans="1:5">
-      <c r="A268" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B268" s="60" t="s">
-        <v>128</v>
-      </c>
-      <c r="C268" s="60"/>
-      <c r="E268" s="52"/>
-    </row>
-    <row r="269" spans="1:5">
-      <c r="A269" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B269" s="59" t="s">
-        <v>127</v>
-      </c>
-      <c r="C269" s="59"/>
-    </row>
-    <row r="270" spans="1:5">
-      <c r="A270" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B270" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C270" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5">
-      <c r="A271" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B271" s="13"/>
-      <c r="C271" s="24" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5">
-      <c r="A272" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="B272" s="13"/>
-      <c r="C272" s="12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3">
-      <c r="A275" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B275" s="65" t="s">
-        <v>114</v>
-      </c>
-      <c r="C275" s="65"/>
-    </row>
-    <row r="276" spans="1:3">
-      <c r="A276" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B276" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="C276" s="60"/>
-    </row>
-    <row r="277" spans="1:3">
-      <c r="A277" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B277" s="59" t="s">
-        <v>133</v>
-      </c>
-      <c r="C277" s="59"/>
-    </row>
-    <row r="278" spans="1:3">
-      <c r="A278" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B278" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C278" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3">
-      <c r="A279" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B279" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C279" s="19" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3">
-      <c r="A280" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B280" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C280" s="19" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3">
-      <c r="A281" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="B281" s="48">
-        <v>18000</v>
-      </c>
-      <c r="C281" s="49" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3">
-      <c r="A282" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="B282" s="47"/>
-      <c r="C282" s="49" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3">
-      <c r="A284" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B284" s="66" t="s">
-        <v>115</v>
-      </c>
-      <c r="C284" s="66"/>
-    </row>
-    <row r="285" spans="1:3">
-      <c r="A285" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B285" s="63" t="s">
-        <v>136</v>
-      </c>
-      <c r="C285" s="63"/>
-    </row>
-    <row r="286" spans="1:3">
-      <c r="A286" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B286" s="64" t="s">
-        <v>127</v>
-      </c>
-      <c r="C286" s="64"/>
-    </row>
-    <row r="287" spans="1:3">
-      <c r="A287" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B287" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C287" s="26" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3">
-      <c r="A288" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="B288" s="27"/>
-      <c r="C288" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5">
-      <c r="A289" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="B289" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="C289" s="28" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5">
-      <c r="A290" s="109" t="s">
-        <v>120</v>
-      </c>
-      <c r="B290" s="110">
-        <v>18000</v>
-      </c>
-      <c r="C290" s="111" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5">
-      <c r="A291" s="109" t="s">
-        <v>130</v>
-      </c>
-      <c r="B291" s="109"/>
-      <c r="C291" s="111" t="s">
-        <v>135</v>
-      </c>
-      <c r="E291" s="50" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5">
-      <c r="E292" s="51"/>
+      <c r="C292" s="94"/>
+      <c r="E292" s="74"/>
     </row>
     <row r="293" spans="1:5">
       <c r="A293" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B293" s="65" t="s">
-        <v>116</v>
-      </c>
-      <c r="C293" s="65"/>
-      <c r="E293" s="51"/>
+        <v>1</v>
+      </c>
+      <c r="B293" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="C293" s="71"/>
+      <c r="E293" s="74"/>
     </row>
     <row r="294" spans="1:5">
       <c r="A294" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B294" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="C294" s="70"/>
+      <c r="E294" s="75"/>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B295" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C295" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B296" s="13"/>
+      <c r="C296" s="24" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B297" s="13"/>
+      <c r="C297" s="12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="E298" s="73" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="E299" s="74"/>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B300" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="C300" s="94"/>
+      <c r="E300" s="74"/>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B294" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="C294" s="60"/>
-      <c r="E294" s="51"/>
-    </row>
-    <row r="295" spans="1:5">
-      <c r="A295" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B295" s="59" t="s">
-        <v>127</v>
-      </c>
-      <c r="C295" s="59"/>
-      <c r="E295" s="51"/>
-    </row>
-    <row r="296" spans="1:5">
-      <c r="A296" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B296" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C296" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E296" s="51"/>
-    </row>
-    <row r="297" spans="1:5">
-      <c r="A297" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B297" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C297" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E297" s="51"/>
-    </row>
-    <row r="298" spans="1:5">
-      <c r="A298" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="B298" s="13"/>
-      <c r="C298" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="E298" s="52"/>
-    </row>
-    <row r="299" spans="1:5">
-      <c r="A299" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="B299" s="48">
-        <v>18000</v>
-      </c>
-      <c r="C299" s="49" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5">
-      <c r="A300" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="B300" s="47"/>
-      <c r="C300" s="49" t="s">
-        <v>135</v>
-      </c>
+      <c r="B301" s="71" t="s">
+        <v>134</v>
+      </c>
+      <c r="C301" s="71"/>
+      <c r="E301" s="74"/>
     </row>
     <row r="302" spans="1:5">
       <c r="A302" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B302" s="70" t="s">
+        <v>133</v>
+      </c>
+      <c r="C302" s="70"/>
+      <c r="E302" s="74"/>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B303" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C303" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E303" s="74"/>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B304" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C304" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E304" s="74"/>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B305" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C305" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E305" s="75"/>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="B306" s="48">
+        <v>18000</v>
+      </c>
+      <c r="C306" s="49" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B307" s="47"/>
+      <c r="C307" s="49" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B302" s="65" t="s">
+      <c r="B309" s="95" t="s">
+        <v>115</v>
+      </c>
+      <c r="C309" s="95"/>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B310" s="96" t="s">
+        <v>136</v>
+      </c>
+      <c r="C310" s="96"/>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B311" s="97" t="s">
+        <v>127</v>
+      </c>
+      <c r="C311" s="97"/>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B312" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C312" s="26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B313" s="27"/>
+      <c r="C313" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B314" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C314" s="28" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="B315" s="65">
+        <v>18000</v>
+      </c>
+      <c r="C315" s="66" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="B316" s="64"/>
+      <c r="C316" s="66" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B318" s="94" t="s">
+        <v>116</v>
+      </c>
+      <c r="C318" s="94"/>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B319" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="C319" s="71"/>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B320" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="C320" s="70"/>
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B321" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C321" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B322" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C322" s="19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B323" s="13"/>
+      <c r="C323" s="19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="B324" s="48">
+        <v>18000</v>
+      </c>
+      <c r="C324" s="49" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B325" s="47"/>
+      <c r="C325" s="49" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B327" s="94" t="s">
         <v>137</v>
       </c>
-      <c r="C302" s="65"/>
-      <c r="E302" s="50" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5">
-      <c r="A303" s="10" t="s">
+      <c r="C327" s="94"/>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B303" s="60" t="s">
+      <c r="B328" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="C303" s="60"/>
-      <c r="E303" s="51"/>
-    </row>
-    <row r="304" spans="1:5">
-      <c r="A304" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B304" s="59" t="s">
-        <v>127</v>
-      </c>
-      <c r="C304" s="59"/>
-      <c r="E304" s="51"/>
-    </row>
-    <row r="305" spans="1:5" ht="14.4" customHeight="1">
-      <c r="A305" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B305" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C305" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E305" s="51"/>
-    </row>
-    <row r="306" spans="1:5">
-      <c r="A306" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B306" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C306" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E306" s="51"/>
-    </row>
-    <row r="307" spans="1:5">
-      <c r="A307" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B307" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C307" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="E307" s="51"/>
-    </row>
-    <row r="308" spans="1:5">
-      <c r="A308" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="B308" s="48"/>
-      <c r="C308" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E308" s="51"/>
-    </row>
-    <row r="309" spans="1:5">
-      <c r="A309" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="B309" s="47"/>
-      <c r="C309" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="E309" s="52"/>
-    </row>
-    <row r="311" spans="1:5">
-      <c r="A311" s="62" t="s">
-        <v>163</v>
-      </c>
-      <c r="B311" s="62"/>
-      <c r="C311" s="62"/>
-    </row>
-    <row r="312" spans="1:5">
-      <c r="A312" s="62"/>
-      <c r="B312" s="62"/>
-      <c r="C312" s="62"/>
-    </row>
-    <row r="313" spans="1:5">
-      <c r="E313" s="50" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5">
-      <c r="A314" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B314" s="65" t="s">
-        <v>144</v>
-      </c>
-      <c r="C314" s="65"/>
-      <c r="E314" s="51"/>
-    </row>
-    <row r="315" spans="1:5">
-      <c r="A315" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B315" s="60" t="s">
-        <v>149</v>
-      </c>
-      <c r="C315" s="60"/>
-      <c r="E315" s="51"/>
-    </row>
-    <row r="316" spans="1:5">
-      <c r="A316" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B316" s="59" t="s">
-        <v>145</v>
-      </c>
-      <c r="C316" s="59"/>
-      <c r="E316" s="51"/>
-    </row>
-    <row r="317" spans="1:5">
-      <c r="A317" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B317" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C317" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E317" s="51"/>
-    </row>
-    <row r="318" spans="1:5">
-      <c r="A318" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B318" s="13"/>
-      <c r="C318" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="E318" s="51"/>
-    </row>
-    <row r="319" spans="1:5">
-      <c r="A319" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="B319" s="13"/>
-      <c r="C319" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="E319" s="51"/>
-    </row>
-    <row r="320" spans="1:5">
-      <c r="A320" s="7"/>
-      <c r="B320" s="8"/>
-      <c r="C320" s="17"/>
-      <c r="E320" s="52"/>
-    </row>
-    <row r="321" spans="1:3">
-      <c r="A321" s="30"/>
-      <c r="B321" s="31"/>
-      <c r="C321" s="17"/>
-    </row>
-    <row r="322" spans="1:3">
-      <c r="A322" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B322" s="65" t="s">
-        <v>151</v>
-      </c>
-      <c r="C322" s="65"/>
-    </row>
-    <row r="323" spans="1:3">
-      <c r="A323" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B323" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="C323" s="60"/>
-    </row>
-    <row r="324" spans="1:3">
-      <c r="A324" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B324" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="C324" s="59"/>
-    </row>
-    <row r="325" spans="1:3">
-      <c r="A325" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B325" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C325" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3">
-      <c r="A326" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="B326" s="13"/>
-      <c r="C326" s="19" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3">
-      <c r="A327" s="7"/>
-      <c r="B327" s="8"/>
-      <c r="C327" s="17"/>
-    </row>
-    <row r="328" spans="1:3">
-      <c r="A328" s="32"/>
-      <c r="B328" s="32"/>
-      <c r="C328" s="32"/>
+      <c r="C328" s="71"/>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B329" s="65" t="s">
-        <v>288</v>
-      </c>
-      <c r="C329" s="65"/>
+        <v>23</v>
+      </c>
+      <c r="B329" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="C329" s="70"/>
     </row>
     <row r="330" spans="1:3">
-      <c r="A330" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B330" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="C330" s="60"/>
+      <c r="A330" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B330" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C330" s="11" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="331" spans="1:3">
-      <c r="A331" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B331" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="C331" s="59"/>
+      <c r="A331" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B331" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C331" s="19" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="332" spans="1:3">
-      <c r="A332" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B332" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C332" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" ht="26.4">
-      <c r="A333" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B333" s="13"/>
-      <c r="C333" s="112" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" ht="26.4">
-      <c r="A334" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B334" s="20"/>
-      <c r="C334" s="113" t="s">
-        <v>314</v>
+      <c r="A332" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B332" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C332" s="19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="B333" s="48"/>
+      <c r="C333" s="29" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B334" s="47"/>
+      <c r="C334" s="49" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="62" t="s">
-        <v>220</v>
-      </c>
-      <c r="B336" s="62"/>
-      <c r="C336" s="62"/>
+      <c r="A336" s="72" t="s">
+        <v>163</v>
+      </c>
+      <c r="B336" s="72"/>
+      <c r="C336" s="72"/>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="62"/>
-      <c r="B337" s="62"/>
-      <c r="C337" s="62"/>
+      <c r="A337" s="72"/>
+      <c r="B337" s="72"/>
+      <c r="C337" s="72"/>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B339" s="65" t="s">
-        <v>219</v>
-      </c>
-      <c r="C339" s="65"/>
+      <c r="B339" s="94" t="s">
+        <v>144</v>
+      </c>
+      <c r="C339" s="94"/>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B340" s="60" t="s">
-        <v>165</v>
-      </c>
-      <c r="C340" s="60"/>
+      <c r="B340" s="71" t="s">
+        <v>149</v>
+      </c>
+      <c r="C340" s="71"/>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B341" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="C341" s="59"/>
+      <c r="B341" s="70" t="s">
+        <v>145</v>
+      </c>
+      <c r="C341" s="70"/>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" s="11" t="s">
@@ -5481,393 +5751,682 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343" s="12" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="B343" s="13"/>
       <c r="C343" s="19" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" ht="27">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3">
       <c r="A344" s="12" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="B344" s="13"/>
       <c r="C344" s="19" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="B345" s="13"/>
-      <c r="C345" s="33" t="s">
-        <v>189</v>
-      </c>
+      <c r="A345" s="7"/>
+      <c r="B345" s="8"/>
+      <c r="C345" s="17"/>
     </row>
     <row r="346" spans="1:3">
-      <c r="A346" s="12"/>
-      <c r="B346" s="13"/>
-      <c r="C346" s="19"/>
-    </row>
-    <row r="347" spans="1:3" ht="15" thickBot="1">
-      <c r="A347" s="14"/>
-      <c r="B347" s="15"/>
-      <c r="C347" s="16"/>
+      <c r="A346" s="30"/>
+      <c r="B346" s="31"/>
+      <c r="C346" s="17"/>
+    </row>
+    <row r="347" spans="1:3">
+      <c r="A347" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B347" s="94" t="s">
+        <v>151</v>
+      </c>
+      <c r="C347" s="94"/>
     </row>
     <row r="348" spans="1:3">
-      <c r="A348" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="B348" s="54"/>
-      <c r="C348" s="55"/>
-    </row>
-    <row r="349" spans="1:3" ht="15" thickBot="1">
-      <c r="A349" s="56"/>
-      <c r="B349" s="57"/>
-      <c r="C349" s="58"/>
+      <c r="A348" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B348" s="71" t="s">
+        <v>152</v>
+      </c>
+      <c r="C348" s="71"/>
+    </row>
+    <row r="349" spans="1:3">
+      <c r="A349" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B349" s="70" t="s">
+        <v>153</v>
+      </c>
+      <c r="C349" s="70"/>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B350" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C350" s="11" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="351" spans="1:3">
-      <c r="A351" s="10" t="s">
+      <c r="A351" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B351" s="13"/>
+      <c r="C351" s="19" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352" s="7"/>
+      <c r="B352" s="8"/>
+      <c r="C352" s="17"/>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" s="32"/>
+      <c r="B353" s="32"/>
+      <c r="C353" s="32"/>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B351" s="59" t="s">
-        <v>177</v>
-      </c>
-      <c r="C351" s="59"/>
-    </row>
-    <row r="352" spans="1:3">
-      <c r="A352" s="10" t="s">
+      <c r="B354" s="94" t="s">
+        <v>288</v>
+      </c>
+      <c r="C354" s="94"/>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B352" s="60" t="s">
-        <v>180</v>
-      </c>
-      <c r="C352" s="60"/>
-    </row>
-    <row r="353" spans="1:3">
-      <c r="A353" s="10" t="s">
+      <c r="B355" s="71" t="s">
+        <v>156</v>
+      </c>
+      <c r="C355" s="71"/>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B353" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="C353" s="59"/>
-    </row>
-    <row r="354" spans="1:3">
-      <c r="A354" s="11" t="s">
+      <c r="B356" s="70" t="s">
+        <v>153</v>
+      </c>
+      <c r="C356" s="70"/>
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B354" s="11" t="s">
+      <c r="B357" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C354" s="11" t="s">
+      <c r="C357" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="1:3">
-      <c r="A355" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="B355" s="13"/>
-      <c r="C355" s="61" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3">
-      <c r="A356" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="B356" s="13"/>
-      <c r="C356" s="61"/>
-    </row>
-    <row r="357" spans="1:3">
-      <c r="A357" s="12"/>
-      <c r="B357" s="13"/>
-      <c r="C357" s="61"/>
-    </row>
-    <row r="358" spans="1:3">
-      <c r="A358" s="20"/>
-      <c r="B358" s="20"/>
-      <c r="C358" s="61"/>
-    </row>
-    <row r="359" spans="1:3" ht="15" thickBot="1"/>
-    <row r="360" spans="1:3">
-      <c r="A360" s="53" t="s">
-        <v>217</v>
-      </c>
-      <c r="B360" s="54"/>
-      <c r="C360" s="55"/>
-    </row>
-    <row r="361" spans="1:3" ht="15" thickBot="1">
-      <c r="A361" s="56"/>
-      <c r="B361" s="57"/>
-      <c r="C361" s="58"/>
-    </row>
-    <row r="363" spans="1:3">
-      <c r="A363" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B363" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="C363" s="59"/>
+    <row r="358" spans="1:3" ht="26.4">
+      <c r="A358" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B358" s="13"/>
+      <c r="C358" s="67" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" ht="26.4">
+      <c r="A359" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B359" s="20"/>
+      <c r="C359" s="68" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361" s="72" t="s">
+        <v>220</v>
+      </c>
+      <c r="B361" s="72"/>
+      <c r="C361" s="72"/>
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362" s="72"/>
+      <c r="B362" s="72"/>
+      <c r="C362" s="72"/>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B364" s="60" t="s">
-        <v>221</v>
-      </c>
-      <c r="C364" s="60"/>
+        <v>0</v>
+      </c>
+      <c r="B364" s="94" t="s">
+        <v>219</v>
+      </c>
+      <c r="C364" s="94"/>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B365" s="71" t="s">
+        <v>165</v>
+      </c>
+      <c r="C365" s="71"/>
+    </row>
+    <row r="366" spans="1:3">
+      <c r="A366" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B365" s="59" t="s">
-        <v>222</v>
-      </c>
-      <c r="C365" s="59"/>
-    </row>
-    <row r="366" spans="1:3">
-      <c r="A366" s="11" t="s">
+      <c r="B366" s="70" t="s">
+        <v>166</v>
+      </c>
+      <c r="C366" s="70"/>
+    </row>
+    <row r="367" spans="1:3">
+      <c r="A367" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B366" s="11" t="s">
+      <c r="B367" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C366" s="11" t="s">
+      <c r="C367" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="367" spans="1:3">
-      <c r="A367" s="41" t="s">
-        <v>223</v>
-      </c>
-      <c r="B367" s="13"/>
-      <c r="C367" s="41" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3" ht="52.8">
-      <c r="A368" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="B368" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="C368" s="42" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="369" spans="1:3">
-      <c r="A369" s="41" t="s">
-        <v>225</v>
+    <row r="368" spans="1:3">
+      <c r="A368" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B368" s="13"/>
+      <c r="C368" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" ht="27">
+      <c r="A369" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="B369" s="13"/>
-      <c r="C369" s="41" t="s">
-        <v>229</v>
+      <c r="C369" s="19" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="370" spans="1:3">
-      <c r="A370" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="B370" s="20"/>
-      <c r="C370" s="41" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" ht="15" thickBot="1"/>
-    <row r="372" spans="1:3">
-      <c r="A372" s="53" t="s">
-        <v>232</v>
-      </c>
-      <c r="B372" s="54"/>
-      <c r="C372" s="55"/>
-    </row>
-    <row r="373" spans="1:3" ht="15" thickBot="1">
-      <c r="A373" s="56"/>
-      <c r="B373" s="57"/>
-      <c r="C373" s="58"/>
-    </row>
-    <row r="375" spans="1:3">
-      <c r="A375" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B375" s="59" t="s">
-        <v>164</v>
-      </c>
-      <c r="C375" s="59"/>
+      <c r="A370" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="B370" s="13"/>
+      <c r="C370" s="33" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3">
+      <c r="A371" s="12"/>
+      <c r="B371" s="13"/>
+      <c r="C371" s="19"/>
+    </row>
+    <row r="372" spans="1:3" ht="15" thickBot="1">
+      <c r="A372" s="14"/>
+      <c r="B372" s="15"/>
+      <c r="C372" s="16"/>
+    </row>
+    <row r="373" spans="1:3">
+      <c r="A373" s="78" t="s">
+        <v>176</v>
+      </c>
+      <c r="B373" s="79"/>
+      <c r="C373" s="80"/>
+    </row>
+    <row r="374" spans="1:3" ht="15" thickBot="1">
+      <c r="A374" s="81"/>
+      <c r="B374" s="82"/>
+      <c r="C374" s="83"/>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B376" s="60" t="s">
-        <v>233</v>
-      </c>
-      <c r="C376" s="60"/>
+        <v>0</v>
+      </c>
+      <c r="B376" s="70" t="s">
+        <v>177</v>
+      </c>
+      <c r="C376" s="70"/>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B377" s="71" t="s">
+        <v>180</v>
+      </c>
+      <c r="C377" s="71"/>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B377" s="59" t="s">
-        <v>234</v>
-      </c>
-      <c r="C377" s="59"/>
-    </row>
-    <row r="378" spans="1:3">
-      <c r="A378" s="11" t="s">
+      <c r="B378" s="70" t="s">
+        <v>166</v>
+      </c>
+      <c r="C378" s="70"/>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B378" s="11" t="s">
+      <c r="B379" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C378" s="11" t="s">
+      <c r="C379" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="15">
-      <c r="A379" t="s">
-        <v>235</v>
-      </c>
-      <c r="B379" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C379" s="41" t="s">
-        <v>236</v>
-      </c>
-    </row>
     <row r="380" spans="1:3">
-      <c r="A380" t="s">
-        <v>238</v>
-      </c>
-      <c r="B380" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="C380" s="41" t="s">
-        <v>236</v>
+      <c r="A380" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B380" s="13"/>
+      <c r="C380" s="98" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="41" t="s">
-        <v>225</v>
+      <c r="A381" s="12" t="s">
+        <v>179</v>
       </c>
       <c r="B381" s="13"/>
-      <c r="C381" s="41" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" ht="15" thickBot="1"/>
-    <row r="384" spans="1:3">
-      <c r="A384" s="53" t="s">
-        <v>240</v>
-      </c>
-      <c r="B384" s="54"/>
-      <c r="C384" s="55"/>
-    </row>
-    <row r="385" spans="1:3" ht="15" thickBot="1">
-      <c r="A385" s="56"/>
-      <c r="B385" s="57"/>
-      <c r="C385" s="58"/>
-    </row>
-    <row r="387" spans="1:3">
-      <c r="A387" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B387" s="59" t="s">
-        <v>241</v>
-      </c>
-      <c r="C387" s="59"/>
+      <c r="C381" s="98"/>
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382" s="12"/>
+      <c r="B382" s="13"/>
+      <c r="C382" s="98"/>
+    </row>
+    <row r="383" spans="1:3">
+      <c r="A383" s="20"/>
+      <c r="B383" s="20"/>
+      <c r="C383" s="98"/>
+    </row>
+    <row r="384" spans="1:3" ht="15" thickBot="1"/>
+    <row r="385" spans="1:3">
+      <c r="A385" s="78" t="s">
+        <v>217</v>
+      </c>
+      <c r="B385" s="79"/>
+      <c r="C385" s="80"/>
+    </row>
+    <row r="386" spans="1:3" ht="15" thickBot="1">
+      <c r="A386" s="81"/>
+      <c r="B386" s="82"/>
+      <c r="C386" s="83"/>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B388" s="60" t="s">
-        <v>242</v>
-      </c>
-      <c r="C388" s="60"/>
+        <v>0</v>
+      </c>
+      <c r="B388" s="70" t="s">
+        <v>218</v>
+      </c>
+      <c r="C388" s="70"/>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B389" s="71" t="s">
+        <v>221</v>
+      </c>
+      <c r="C389" s="71"/>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B389" s="59" t="s">
-        <v>234</v>
-      </c>
-      <c r="C389" s="59"/>
-    </row>
-    <row r="390" spans="1:3">
-      <c r="A390" s="11" t="s">
+      <c r="B390" s="70" t="s">
+        <v>222</v>
+      </c>
+      <c r="C390" s="70"/>
+    </row>
+    <row r="391" spans="1:3">
+      <c r="A391" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B390" s="45" t="s">
+      <c r="B391" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C390" s="11" t="s">
+      <c r="C391" s="11" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3">
-      <c r="A391" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="B391" t="s">
-        <v>244</v>
-      </c>
-      <c r="C391" s="41" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="B392" s="13"/>
+      <c r="C392" s="41" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" ht="52.8">
+      <c r="A393" s="42" t="s">
+        <v>224</v>
+      </c>
+      <c r="B393" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="C393" s="42" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="B394" s="13"/>
+      <c r="C394" s="41" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3">
+      <c r="A395" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="B395" s="20"/>
+      <c r="C395" s="41" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" ht="15" thickBot="1"/>
+    <row r="397" spans="1:3">
+      <c r="A397" s="78" t="s">
+        <v>232</v>
+      </c>
+      <c r="B397" s="79"/>
+      <c r="C397" s="80"/>
+    </row>
+    <row r="398" spans="1:3" ht="15" thickBot="1">
+      <c r="A398" s="81"/>
+      <c r="B398" s="82"/>
+      <c r="C398" s="83"/>
+    </row>
+    <row r="400" spans="1:3">
+      <c r="A400" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B400" s="70" t="s">
+        <v>164</v>
+      </c>
+      <c r="C400" s="70"/>
+    </row>
+    <row r="401" spans="1:3">
+      <c r="A401" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B401" s="71" t="s">
+        <v>233</v>
+      </c>
+      <c r="C401" s="71"/>
+    </row>
+    <row r="402" spans="1:3">
+      <c r="A402" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B402" s="70" t="s">
+        <v>234</v>
+      </c>
+      <c r="C402" s="70"/>
+    </row>
+    <row r="403" spans="1:3">
+      <c r="A403" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B403" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C403" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" ht="15">
+      <c r="A404" t="s">
+        <v>235</v>
+      </c>
+      <c r="B404" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="C404" s="41" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3">
+      <c r="A405" t="s">
+        <v>238</v>
+      </c>
+      <c r="B405" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="C405" s="41" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3">
+      <c r="A406" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="B406" s="13"/>
+      <c r="C406" s="41" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" ht="15" thickBot="1"/>
+    <row r="409" spans="1:3">
+      <c r="A409" s="78" t="s">
+        <v>240</v>
+      </c>
+      <c r="B409" s="79"/>
+      <c r="C409" s="80"/>
+    </row>
+    <row r="410" spans="1:3" ht="15" thickBot="1">
+      <c r="A410" s="81"/>
+      <c r="B410" s="82"/>
+      <c r="C410" s="83"/>
+    </row>
+    <row r="412" spans="1:3">
+      <c r="A412" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B412" s="70" t="s">
+        <v>241</v>
+      </c>
+      <c r="C412" s="70"/>
+    </row>
+    <row r="413" spans="1:3">
+      <c r="A413" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B413" s="71" t="s">
+        <v>242</v>
+      </c>
+      <c r="C413" s="71"/>
+    </row>
+    <row r="414" spans="1:3">
+      <c r="A414" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B414" s="70" t="s">
+        <v>234</v>
+      </c>
+      <c r="C414" s="70"/>
+    </row>
+    <row r="415" spans="1:3">
+      <c r="A415" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B415" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="C415" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3">
+      <c r="A416" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="B416" t="s">
+        <v>244</v>
+      </c>
+      <c r="C416" s="41" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3">
+      <c r="A417" s="41" t="s">
         <v>245</v>
       </c>
-      <c r="B392" s="46" t="s">
+      <c r="B417" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C392" s="41" t="s">
+      <c r="C417" s="41" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="393" spans="1:3">
-      <c r="A393" s="41" t="s">
+    <row r="418" spans="1:3">
+      <c r="A418" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="B393" s="44"/>
-      <c r="C393" s="41" t="s">
+      <c r="B418" s="44"/>
+      <c r="C418" s="41" t="s">
         <v>247</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="157">
-    <mergeCell ref="B211:C211"/>
-    <mergeCell ref="B197:C197"/>
-    <mergeCell ref="B198:C198"/>
-    <mergeCell ref="B202:C202"/>
-    <mergeCell ref="B203:C203"/>
-    <mergeCell ref="B204:C204"/>
-    <mergeCell ref="B209:C209"/>
-    <mergeCell ref="B210:C210"/>
-    <mergeCell ref="B182:C182"/>
-    <mergeCell ref="B183:C183"/>
-    <mergeCell ref="B181:C181"/>
-    <mergeCell ref="B189:C189"/>
-    <mergeCell ref="B190:C190"/>
-    <mergeCell ref="B191:C191"/>
-    <mergeCell ref="B196:C196"/>
-    <mergeCell ref="B167:C167"/>
-    <mergeCell ref="B168:C168"/>
-    <mergeCell ref="B169:C169"/>
-    <mergeCell ref="B174:C174"/>
-    <mergeCell ref="B175:C175"/>
-    <mergeCell ref="B176:C176"/>
+  <mergeCells count="164">
+    <mergeCell ref="B233:C233"/>
+    <mergeCell ref="B234:C234"/>
+    <mergeCell ref="B232:C232"/>
+    <mergeCell ref="B222:C222"/>
+    <mergeCell ref="A216:C217"/>
+    <mergeCell ref="E246:E253"/>
+    <mergeCell ref="A409:C410"/>
+    <mergeCell ref="B412:C412"/>
+    <mergeCell ref="B413:C413"/>
+    <mergeCell ref="B414:C414"/>
+    <mergeCell ref="E298:E305"/>
+    <mergeCell ref="E287:E294"/>
+    <mergeCell ref="E276:E283"/>
+    <mergeCell ref="A385:C386"/>
+    <mergeCell ref="B388:C388"/>
+    <mergeCell ref="B389:C389"/>
+    <mergeCell ref="B390:C390"/>
+    <mergeCell ref="A397:C398"/>
+    <mergeCell ref="B400:C400"/>
+    <mergeCell ref="B401:C401"/>
+    <mergeCell ref="B402:C402"/>
+    <mergeCell ref="B377:C377"/>
+    <mergeCell ref="B378:C378"/>
+    <mergeCell ref="C380:C383"/>
+    <mergeCell ref="A373:C374"/>
+    <mergeCell ref="B376:C376"/>
+    <mergeCell ref="A361:C362"/>
+    <mergeCell ref="B364:C364"/>
+    <mergeCell ref="B365:C365"/>
+    <mergeCell ref="B366:C366"/>
+    <mergeCell ref="B339:C339"/>
+    <mergeCell ref="B340:C340"/>
+    <mergeCell ref="B341:C341"/>
+    <mergeCell ref="B347:C347"/>
+    <mergeCell ref="B348:C348"/>
+    <mergeCell ref="B349:C349"/>
+    <mergeCell ref="B328:C328"/>
+    <mergeCell ref="B329:C329"/>
+    <mergeCell ref="A336:C337"/>
+    <mergeCell ref="B354:C354"/>
+    <mergeCell ref="B355:C355"/>
+    <mergeCell ref="B356:C356"/>
+    <mergeCell ref="B310:C310"/>
+    <mergeCell ref="B311:C311"/>
+    <mergeCell ref="B318:C318"/>
+    <mergeCell ref="B319:C319"/>
+    <mergeCell ref="B320:C320"/>
+    <mergeCell ref="B327:C327"/>
+    <mergeCell ref="B293:C293"/>
+    <mergeCell ref="B294:C294"/>
+    <mergeCell ref="B300:C300"/>
+    <mergeCell ref="B301:C301"/>
+    <mergeCell ref="B302:C302"/>
+    <mergeCell ref="B309:C309"/>
+    <mergeCell ref="B254:C254"/>
+    <mergeCell ref="A280:C281"/>
+    <mergeCell ref="B283:C283"/>
+    <mergeCell ref="B284:C284"/>
+    <mergeCell ref="B285:C285"/>
+    <mergeCell ref="B292:C292"/>
+    <mergeCell ref="B275:C275"/>
+    <mergeCell ref="B276:C276"/>
+    <mergeCell ref="B255:C255"/>
+    <mergeCell ref="B260:C260"/>
+    <mergeCell ref="B261:C261"/>
+    <mergeCell ref="B262:C262"/>
+    <mergeCell ref="B268:C268"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="A243:C244"/>
+    <mergeCell ref="B269:C269"/>
+    <mergeCell ref="B270:C270"/>
+    <mergeCell ref="B274:C274"/>
+    <mergeCell ref="B246:C246"/>
+    <mergeCell ref="B247:C247"/>
+    <mergeCell ref="B248:C248"/>
+    <mergeCell ref="B253:C253"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B220:C220"/>
+    <mergeCell ref="B221:C221"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="A86:C87"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="A158:C159"/>
     <mergeCell ref="B161:C161"/>
     <mergeCell ref="B162:C162"/>
@@ -5892,118 +6451,27 @@
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="A86:C87"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="A218:C219"/>
-    <mergeCell ref="B244:C244"/>
-    <mergeCell ref="B245:C245"/>
-    <mergeCell ref="B249:C249"/>
-    <mergeCell ref="B221:C221"/>
-    <mergeCell ref="B222:C222"/>
-    <mergeCell ref="B223:C223"/>
-    <mergeCell ref="B228:C228"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B268:C268"/>
-    <mergeCell ref="B269:C269"/>
-    <mergeCell ref="B275:C275"/>
-    <mergeCell ref="B276:C276"/>
-    <mergeCell ref="B277:C277"/>
-    <mergeCell ref="B284:C284"/>
-    <mergeCell ref="B229:C229"/>
-    <mergeCell ref="A255:C256"/>
-    <mergeCell ref="B258:C258"/>
-    <mergeCell ref="B259:C259"/>
-    <mergeCell ref="B260:C260"/>
-    <mergeCell ref="B267:C267"/>
-    <mergeCell ref="B250:C250"/>
-    <mergeCell ref="B251:C251"/>
-    <mergeCell ref="B230:C230"/>
-    <mergeCell ref="B235:C235"/>
-    <mergeCell ref="B236:C236"/>
-    <mergeCell ref="B237:C237"/>
-    <mergeCell ref="B243:C243"/>
-    <mergeCell ref="B303:C303"/>
-    <mergeCell ref="B304:C304"/>
-    <mergeCell ref="A311:C312"/>
-    <mergeCell ref="B329:C329"/>
-    <mergeCell ref="B330:C330"/>
-    <mergeCell ref="B331:C331"/>
-    <mergeCell ref="B285:C285"/>
-    <mergeCell ref="B286:C286"/>
-    <mergeCell ref="B293:C293"/>
-    <mergeCell ref="B294:C294"/>
-    <mergeCell ref="B295:C295"/>
-    <mergeCell ref="B302:C302"/>
-    <mergeCell ref="B339:C339"/>
-    <mergeCell ref="B340:C340"/>
-    <mergeCell ref="B341:C341"/>
-    <mergeCell ref="B314:C314"/>
-    <mergeCell ref="B315:C315"/>
-    <mergeCell ref="B316:C316"/>
-    <mergeCell ref="B322:C322"/>
-    <mergeCell ref="B323:C323"/>
-    <mergeCell ref="B324:C324"/>
-    <mergeCell ref="E261:E268"/>
-    <mergeCell ref="A384:C385"/>
-    <mergeCell ref="B387:C387"/>
-    <mergeCell ref="B388:C388"/>
-    <mergeCell ref="B389:C389"/>
-    <mergeCell ref="E313:E320"/>
-    <mergeCell ref="E302:E309"/>
-    <mergeCell ref="E291:E298"/>
-    <mergeCell ref="A360:C361"/>
-    <mergeCell ref="B363:C363"/>
-    <mergeCell ref="B364:C364"/>
-    <mergeCell ref="B365:C365"/>
-    <mergeCell ref="A372:C373"/>
-    <mergeCell ref="B375:C375"/>
-    <mergeCell ref="B376:C376"/>
-    <mergeCell ref="B377:C377"/>
-    <mergeCell ref="B352:C352"/>
-    <mergeCell ref="B353:C353"/>
-    <mergeCell ref="C355:C358"/>
-    <mergeCell ref="A348:C349"/>
-    <mergeCell ref="B351:C351"/>
-    <mergeCell ref="A336:C337"/>
+    <mergeCell ref="B181:C181"/>
+    <mergeCell ref="B189:C189"/>
+    <mergeCell ref="B190:C190"/>
+    <mergeCell ref="B191:C191"/>
+    <mergeCell ref="B196:C196"/>
+    <mergeCell ref="B167:C167"/>
+    <mergeCell ref="B168:C168"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="B174:C174"/>
+    <mergeCell ref="B175:C175"/>
+    <mergeCell ref="B176:C176"/>
+    <mergeCell ref="B211:C211"/>
+    <mergeCell ref="B197:C197"/>
+    <mergeCell ref="B198:C198"/>
+    <mergeCell ref="B202:C202"/>
+    <mergeCell ref="B203:C203"/>
+    <mergeCell ref="B204:C204"/>
+    <mergeCell ref="B209:C209"/>
+    <mergeCell ref="B210:C210"/>
+    <mergeCell ref="B182:C182"/>
+    <mergeCell ref="B183:C183"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6026,34 +6494,34 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="99" t="s">
         <v>182</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="98"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="101"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="106" t="s">
         <v>183</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="106" t="s">
         <v>184</v>
       </c>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -6073,22 +6541,22 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15">
-      <c r="A5" s="82" t="s">
+      <c r="A5" s="54" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="82" t="s">
+      <c r="B5" s="54" t="s">
         <v>188</v>
       </c>
       <c r="C5" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="86" t="s">
+      <c r="D5" s="114" t="s">
         <v>194</v>
       </c>
       <c r="E5" s="41"/>
     </row>
     <row r="6" spans="1:5" ht="15">
-      <c r="A6" s="82" t="s">
+      <c r="A6" s="54" t="s">
         <v>186</v>
       </c>
       <c r="B6" s="41" t="s">
@@ -6097,25 +6565,25 @@
       <c r="C6" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="86"/>
+      <c r="D6" s="114"/>
       <c r="E6" s="41"/>
     </row>
     <row r="7" spans="1:5" ht="15">
-      <c r="A7" s="82" t="s">
+      <c r="A7" s="54" t="s">
         <v>190</v>
       </c>
-      <c r="B7" s="82" t="s">
+      <c r="B7" s="54" t="s">
         <v>188</v>
       </c>
       <c r="C7" s="41"/>
-      <c r="D7" s="86"/>
+      <c r="D7" s="114"/>
       <c r="E7" s="41"/>
     </row>
     <row r="8" spans="1:5" ht="15">
-      <c r="A8" s="82" t="s">
+      <c r="A8" s="54" t="s">
         <v>191</v>
       </c>
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="54" t="s">
         <v>189</v>
       </c>
       <c r="C8" s="41" t="s">
@@ -6128,34 +6596,34 @@
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="93" t="s">
+      <c r="B16" s="111" t="s">
         <v>195</v>
       </c>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="95"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="113"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="83" t="s">
+      <c r="B17" s="106" t="s">
         <v>196</v>
       </c>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
+      <c r="C17" s="106"/>
+      <c r="D17" s="106"/>
+      <c r="E17" s="106"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="92" t="s">
+      <c r="B18" s="115" t="s">
         <v>197</v>
       </c>
-      <c r="C18" s="83"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="106"/>
+      <c r="E18" s="106"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
@@ -6175,91 +6643,91 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="15">
-      <c r="A20" s="82" t="s">
+      <c r="A20" s="54" t="s">
         <v>198</v>
       </c>
       <c r="B20" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="C20" s="85" t="s">
+      <c r="C20" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="D20" s="86" t="s">
+      <c r="D20" s="114" t="s">
         <v>194</v>
       </c>
       <c r="E20" s="41"/>
     </row>
     <row r="21" spans="1:5" ht="28.8">
-      <c r="A21" s="82" t="s">
+      <c r="A21" s="54" t="s">
         <v>199</v>
       </c>
       <c r="B21" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="C21" s="87" t="s">
+      <c r="C21" s="56" t="s">
         <v>207</v>
       </c>
-      <c r="D21" s="86"/>
+      <c r="D21" s="114"/>
       <c r="E21" s="41"/>
     </row>
     <row r="22" spans="1:5" ht="43.2">
-      <c r="A22" s="88" t="s">
+      <c r="A22" s="57" t="s">
         <v>200</v>
       </c>
-      <c r="B22" s="87" t="s">
+      <c r="B22" s="56" t="s">
         <v>204</v>
       </c>
-      <c r="C22" s="85" t="s">
+      <c r="C22" s="55" t="s">
         <v>208</v>
       </c>
-      <c r="D22" s="86"/>
+      <c r="D22" s="114"/>
       <c r="E22" s="41"/>
     </row>
     <row r="23" spans="1:5" ht="43.2">
-      <c r="A23" s="114" t="s">
+      <c r="A23" s="69" t="s">
         <v>201</v>
       </c>
-      <c r="B23" s="108" t="s">
+      <c r="B23" s="63" t="s">
         <v>205</v>
       </c>
-      <c r="C23" s="108" t="s">
+      <c r="C23" s="63" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="86"/>
+      <c r="D23" s="114"/>
       <c r="E23" s="41"/>
     </row>
     <row r="38" spans="1:5" ht="15.6">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="89" t="s">
+      <c r="B38" s="108" t="s">
         <v>291</v>
       </c>
-      <c r="C38" s="90"/>
-      <c r="D38" s="90"/>
-      <c r="E38" s="91"/>
+      <c r="C38" s="109"/>
+      <c r="D38" s="109"/>
+      <c r="E38" s="110"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="83" t="s">
+      <c r="B39" s="106" t="s">
         <v>289</v>
       </c>
-      <c r="C39" s="83"/>
-      <c r="D39" s="83"/>
-      <c r="E39" s="83"/>
+      <c r="C39" s="106"/>
+      <c r="D39" s="106"/>
+      <c r="E39" s="106"/>
     </row>
     <row r="40" spans="1:5" ht="34.799999999999997" customHeight="1">
-      <c r="A40" s="81" t="s">
+      <c r="A40" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="84" t="s">
+      <c r="B40" s="107" t="s">
         <v>290</v>
       </c>
-      <c r="C40" s="84"/>
-      <c r="D40" s="84"/>
-      <c r="E40" s="84"/>
+      <c r="C40" s="107"/>
+      <c r="D40" s="107"/>
+      <c r="E40" s="107"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
@@ -6279,7 +6747,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" ht="30">
-      <c r="A42" s="100" t="s">
+      <c r="A42" s="58" t="s">
         <v>292</v>
       </c>
       <c r="B42" s="42" t="s">
@@ -6288,13 +6756,13 @@
       <c r="C42" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="D42" s="105" t="s">
+      <c r="D42" s="103" t="s">
         <v>194</v>
       </c>
-      <c r="E42" s="99"/>
+      <c r="E42" s="102"/>
     </row>
     <row r="43" spans="1:5" ht="28.8">
-      <c r="A43" s="100" t="s">
+      <c r="A43" s="58" t="s">
         <v>294</v>
       </c>
       <c r="B43" s="42" t="s">
@@ -6303,11 +6771,11 @@
       <c r="C43" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="D43" s="106"/>
-      <c r="E43" s="99"/>
+      <c r="D43" s="104"/>
+      <c r="E43" s="102"/>
     </row>
     <row r="44" spans="1:5" ht="15">
-      <c r="A44" s="100" t="s">
+      <c r="A44" s="58" t="s">
         <v>295</v>
       </c>
       <c r="B44" s="42" t="s">
@@ -6316,33 +6784,33 @@
       <c r="C44" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="D44" s="106"/>
-      <c r="E44" s="99"/>
+      <c r="D44" s="104"/>
+      <c r="E44" s="102"/>
     </row>
     <row r="45" spans="1:5" ht="28.8">
-      <c r="A45" s="101" t="s">
+      <c r="A45" s="59" t="s">
         <v>296</v>
       </c>
-      <c r="B45" s="102" t="s">
+      <c r="B45" s="60" t="s">
         <v>300</v>
       </c>
-      <c r="C45" s="102" t="s">
+      <c r="C45" s="60" t="s">
         <v>302</v>
       </c>
-      <c r="D45" s="106"/>
-      <c r="E45" s="99"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="102"/>
     </row>
     <row r="46" spans="1:5" ht="15">
-      <c r="A46" s="103" t="s">
+      <c r="A46" s="61" t="s">
         <v>297</v>
       </c>
-      <c r="B46" s="104" t="s">
+      <c r="B46" s="62" t="s">
         <v>301</v>
       </c>
       <c r="C46" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="D46" s="107"/>
+      <c r="D46" s="105"/>
       <c r="E46" s="41"/>
     </row>
   </sheetData>
